--- a/cidadesss.xlsx
+++ b/cidadesss.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="13" uniqueCount="13">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="705" uniqueCount="705">
   <x:si>
     <x:t>Populaçao estimada</x:t>
   </x:si>
@@ -22,21 +22,426 @@
     <x:t>população no ultimo censo</x:t>
   </x:si>
   <x:si>
-    <x:t xml:space="preserve">densidade demografica </x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">codigo do municipio </x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">gentilico </x:t>
-  </x:si>
-  <x:si>
-    <x:t xml:space="preserve">prefeito </x:t>
+    <x:t>densidade demografica</x:t>
+  </x:si>
+  <x:si>
+    <x:t>codigo do municipio</x:t>
+  </x:si>
+  <x:si>
+    <x:t>gentilico</x:t>
+  </x:si>
+  <x:si>
+    <x:t>prefeito</x:t>
   </x:si>
   <x:si>
     <x:t>Codigos</x:t>
   </x:si>
   <x:si>
+    <x:t>CEP</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Cidade</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6.704
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7,61
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3100104</x:t>
+  </x:si>
+  <x:si>
+    <x:t>abadiense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WANDERLEI LEMES SANTOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1</x:t>
+  </x:si>
+  <x:si>
+    <x:t>38540-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Abadia dos Dourados</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23250</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.690
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12,49
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3100203</x:t>
+  </x:si>
+  <x:si>
+    <x:t>abaetense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>IVANIR DELADIER DA COSTA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35620-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Abaeté</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12335</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11.885
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8,79
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3155504</x:t>
+  </x:si>
+  <x:si>
+    <x:t>rio-paraibano</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VALDEMIR DIOGENES DA SILVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>38812-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Rio Paranaíba</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13444</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13.311
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28,29
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3100302</x:t>
+  </x:si>
+  <x:si>
+    <x:t>abre-campense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VITOR HENRIQUE MOREIRA FERREIRA DE OLIVEIRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35365-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Abre Campo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3994</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3.920
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>38,47
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3100401</x:t>
+  </x:si>
+  <x:si>
+    <x:t>acaiaquense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LUIZ CARLOS FAUSTINO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35438-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Acaiaca</x:t>
+  </x:si>
+  <x:si>
+    <x:t>52446</x:t>
+  </x:si>
+  <x:si>
+    <x:t>45.449
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>83,76
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3131901</x:t>
+  </x:si>
+  <x:si>
+    <x:t>itabiritense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ORLANDO AMORIM CALDEIRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35458-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Itabirito</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6288</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6.497
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4,14
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3108503</x:t>
+  </x:si>
+  <x:si>
+    <x:t>botumiriense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANA PEREIRA NETA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>39597-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Botumirim</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25141</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24.959
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18,50
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3101102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>aimorense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARCELO MARQUES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35200-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Aimorés</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5976</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6.162
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9,48
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3101201</x:t>
+  </x:si>
+  <x:si>
+    <x:t>aiuruocano</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ERLISSON VITOR LOPES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>37450-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Aiuruoca</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2665</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2.709
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16,79
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3101300</x:t>
+  </x:si>
+  <x:si>
+    <x:t>alagoense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JULIANO DINIZ DE OLIVEIRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>37458-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Alagoa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3011</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2.913
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>50,22
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3101409</x:t>
+  </x:si>
+  <x:si>
+    <x:t>albertinense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JOÃO PAULO FACANALI DE OLIVEIRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>37596-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Albertina</x:t>
+  </x:si>
+  <x:si>
+    <x:t>13443</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.611
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12,03
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3140506</x:t>
+  </x:si>
+  <x:si>
+    <x:t>martinho-campense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WILSON CORREA ALVES AFONSO DE CARVALHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35608-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Martinho Campos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>67822</x:t>
+  </x:si>
+  <x:si>
+    <x:t>65.128
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43,36
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3126109</x:t>
+  </x:si>
+  <x:si>
+    <x:t>formiguense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUGÊNIO VILELA JÚNIOR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35579-400</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Formiga</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22949</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.242
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14,99
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3118403</x:t>
+  </x:si>
+  <x:si>
+    <x:t>conselheiro-penense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NADIA FILOMENA DUTRA FRANCA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35245-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Conselheiro Pena</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27966</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.547
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8,31
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3119302</x:t>
+  </x:si>
+  <x:si>
+    <x:t>coromandelense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FERNANDO BRENO VALADARES VIEIRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>38560-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Coromandel</x:t>
+  </x:si>
+  <x:si>
     <x:t>39690</x:t>
   </x:si>
   <x:si>
@@ -55,6 +460,1845 @@
   </x:si>
   <x:si>
     <x:t>CLAUDIO TOMAZ DE FREITAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>38282-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Iturama</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20418</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.134
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15,37
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3134608</x:t>
+  </x:si>
+  <x:si>
+    <x:t>jaboticatubense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ENEIMAR ADRIANO MARQUES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35835-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Jaboticatubas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7436</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7.172
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>42,95
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3101805</x:t>
+  </x:si>
+  <x:si>
+    <x:t>alpercatense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RAFAEL AUGUSTO FRANCA OLIVEIRA MACHADO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35138-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Alpercata</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19958</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18.488
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>40,66
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3101904</x:t>
+  </x:si>
+  <x:si>
+    <x:t>alpinopolense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RAFAEL HENRIQUE DA SILVA FREIRE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>37940-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Alpinópolis</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35210-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>281046</x:t>
+  </x:si>
+  <x:si>
+    <x:t>263.689
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>112,58
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3127701</x:t>
+  </x:si>
+  <x:si>
+    <x:t>valadarense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANDRÉ LUIZ COELHO MERLO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35102-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Governador Valadares</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7766</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.012
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10,61
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3553500</x:t>
+  </x:si>
+  <x:si>
+    <x:t>tapiraiense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARALDO TODESCO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>38985-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Tapiraí</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3844</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.444
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15,98
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3102209</x:t>
+  </x:si>
+  <x:si>
+    <x:t>alvarenguense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DIOCÉLIO FERNANDO RIBEIRO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35249-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Alvarenga</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15169</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.261
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25,46
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3102308</x:t>
+  </x:si>
+  <x:si>
+    <x:t>alvinopolense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MAUROSAN GONÇALVES MACHADO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35950-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Alvinópolis</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7803</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7.913
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14,23
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3105004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>baldinense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FABRICIO ANDRADE MAGALHÃES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35734-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Baldim</x:t>
+  </x:si>
+  <x:si>
+    <x:t>117825</x:t>
+  </x:si>
+  <x:si>
+    <x:t>109.801
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>40,23
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3103504</x:t>
+  </x:si>
+  <x:si>
+    <x:t>araguarino</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RENATO CARVALHO FERNANDES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>38455-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Araguari</x:t>
+  </x:si>
+  <x:si>
+    <x:t>74558</x:t>
+  </x:si>
+  <x:si>
+    <x:t>70.281
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>56,41
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3146107</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ouro-pretano</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANGELO OSWALDO DE ARAUJO SANTOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35412-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ouro Preto</x:t>
+  </x:si>
+  <x:si>
+    <x:t>41396</x:t>
+  </x:si>
+  <x:si>
+    <x:t>37.270
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>79,40
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3102605</x:t>
+  </x:si>
+  <x:si>
+    <x:t>andradense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARGOT NAVARRO GRAZIANI PIOLI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>37795-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Andradas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8557</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.003
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43,21
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3102852</x:t>
+  </x:si>
+  <x:si>
+    <x:t>angelandense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JOÃO PAULO BATISTA DE SOUZA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>39685-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Angelândia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>80616</x:t>
+  </x:si>
+  <x:si>
+    <x:t>74.219
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22,50
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3120904</x:t>
+  </x:si>
+  <x:si>
+    <x:t>curvelano</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LUIZ PAULO GLORIA GUIMARAES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35798-400</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Curvelo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11005</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.264
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>42,43
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3130200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>igaratinguense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FABIO ALVES COSTA FONSECA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35698-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Igaratinga</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9275</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.565
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12,15
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3103009</x:t>
+  </x:si>
+  <x:si>
+    <x:t>antônio-diense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BENEDITO DE ASSIS LIMA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35177-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Antônio Dias</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5338</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5.800
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8,09
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3126752</x:t>
+  </x:si>
+  <x:si>
+    <x:t>franciscopolitano</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NILTON DOS SANTOS COIMBRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>39697-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Franciscópolis</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35411-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>45047</x:t>
+  </x:si>
+  <x:si>
+    <x:t>40.750
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>75,11
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3110004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>caeteense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LUCAS COELHO FERREIRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>34960-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Caeté</x:t>
+  </x:si>
+  <x:si>
+    <x:t>60012</x:t>
+  </x:si>
+  <x:si>
+    <x:t>53.468
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22,03
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3127107</x:t>
+  </x:si>
+  <x:si>
+    <x:t>frutalense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BRUNO AUGUSTO DE JESUS FERREIRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>38208-300</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Frutal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9368</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.276
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12,60
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3100500</x:t>
+  </x:si>
+  <x:si>
+    <x:t>açucenense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RAULISSON MORAIS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35147-100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Açucena</x:t>
+  </x:si>
+  <x:si>
+    <x:t>40666</x:t>
+  </x:si>
+  <x:si>
+    <x:t>33.973
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>53,13
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3109006</x:t>
+  </x:si>
+  <x:si>
+    <x:t>brumadinhense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AVIMAR DE MELO BARCELOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35462-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Brumadinho</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2787</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2.823
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31,57
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3103603</x:t>
+  </x:si>
+  <x:si>
+    <x:t>arantinense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDIMAR LUIS DE OLIVEIRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>37360-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Arantina</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6931</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6.144
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20,77
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3103751</x:t>
+  </x:si>
+  <x:si>
+    <x:t>araporense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RENATA CRISTINA SILVA BORGES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>38465-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Araporã</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2835</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2.775
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15,96
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3103801</x:t>
+  </x:si>
+  <x:si>
+    <x:t>arapuaense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JOAO BATISTA TERTO DA CUNHA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>38860-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Arapuá</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2354</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2.243
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12,02
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3103207</x:t>
+  </x:si>
+  <x:si>
+    <x:t>araçaiense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARCIO GONZAGA DIAS DE OLIVEIRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35777-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Araçaí</x:t>
+  </x:si>
+  <x:si>
+    <x:t>36712</x:t>
+  </x:si>
+  <x:si>
+    <x:t>36.013
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16,10
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3103405</x:t>
+  </x:si>
+  <x:si>
+    <x:t>araçuaiense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>TADEU BARBOSA DE OLIVEIRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>39600-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Araçuaí</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9401</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7.883
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>32,11
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3103900</x:t>
+  </x:si>
+  <x:si>
+    <x:t>araujense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GERALDO MAGELA DA SILVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35603-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Araújos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10883</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9.509
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>58,38
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3104106</x:t>
+  </x:si>
+  <x:si>
+    <x:t>arceburguense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GILSON PEREIRA DE MELLO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>37820-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Arceburgo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>40380</x:t>
+  </x:si>
+  <x:si>
+    <x:t>36.597
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>71,78
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3104205</x:t>
+  </x:si>
+  <x:si>
+    <x:t>arcoense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>CLAUDENIR JOSÉ DE MELO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35588-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Arcos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25358</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23.218
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8,59
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3129509</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ibiaense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARLENE APARECIDA DE SOUZA SILVA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>38955-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ibiá</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5269</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.770
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19,60
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3104452</x:t>
+  </x:si>
+  <x:si>
+    <x:t>aricanduvense ou aricanduvano</x:t>
+  </x:si>
+  <x:si>
+    <x:t>VALDEIR SANTOS COIMBRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>39678-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Aricanduva</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17862</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.674
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,35
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3104502</x:t>
+  </x:si>
+  <x:si>
+    <x:t>arinense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARCÍLIO ÁLISSON FONSECA DE ALMEIDA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>38680-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Arinos</x:t>
+  </x:si>
+  <x:si>
+    <x:t>94808</x:t>
+  </x:si>
+  <x:si>
+    <x:t>84.215
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>152,77
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3147105</x:t>
+  </x:si>
+  <x:si>
+    <x:t>pará-minense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ELIAS DINIZ</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35665-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Pará de Minas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31364</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.856
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>92,02
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3140704</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mateus-lemense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>RENILTON RIBEIRO COELHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35672-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mateus Leme</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35147-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7131</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6.830
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4,95
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3121209</x:t>
+  </x:si>
+  <x:si>
+    <x:t>delfinopolitano</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SUELY ALVES FERREIRA LEMOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>37915-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Delfinópolis</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19199</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18.307
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24,39
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3104908</x:t>
+  </x:si>
+  <x:si>
+    <x:t>baependiano</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DOUGLAS STADUTO SOUZA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>37443-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Baependi</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35105-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>337092</x:t>
+  </x:si>
+  <x:si>
+    <x:t>295.988
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>65,43
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3170107</x:t>
+  </x:si>
+  <x:si>
+    <x:t>uberabense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ELISA GONÇALVES DE ARAÚJO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>38101-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Uberaba</x:t>
+  </x:si>
+  <x:si>
+    <x:t>39652-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Minas Novas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35579-200</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35732-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>71551</x:t>
+  </x:si>
+  <x:si>
+    <x:t>60.271
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>66,20
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3124104</x:t>
+  </x:si>
+  <x:si>
+    <x:t>esmeraldense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>MARCELO NONATO FIGUEIREDO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>32813-500</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Esmeraldas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23898</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22.734
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15,62
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3105103</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bambuiense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>OLIVIO JOSÉ TEIXEIRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>38900-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bambuí</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5778</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5.338
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>113,41
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3105301</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bandeirante-do-sul</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDERVAN LEANDRO DE FREITAS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>37740-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bandeira do Sul</x:t>
+  </x:si>
+  <x:si>
+    <x:t>61288</x:t>
+  </x:si>
+  <x:si>
+    <x:t>54.219
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>45,40
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3140001</x:t>
+  </x:si>
+  <x:si>
+    <x:t>marianense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>-</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35423-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mariana</x:t>
+  </x:si>
+  <x:si>
+    <x:t>265409</x:t>
+  </x:si>
+  <x:si>
+    <x:t>239.468
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.452,34
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3131307</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ipatinguense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>GUSTAVO MORAIS NUNES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35165-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Ipatinga</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20883</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19.064
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>55,15
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2927507</x:t>
+  </x:si>
+  <x:si>
+    <x:t>barbarense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDIFRANCIO DE JESUS OLIVEIRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35963-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Santa Bárbara</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5015</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6.143
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16,01
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3105707</x:t>
+  </x:si>
+  <x:si>
+    <x:t>barra-longuense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>FERNANDO JOSÉ CARNEIRO MAGALHÃES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35447-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Barra Longa</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27647</x:t>
+  </x:si>
+  <x:si>
+    <x:t>27.111
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>39,57
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3139607</x:t>
+  </x:si>
+  <x:si>
+    <x:t>mantenense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JOÃO RUFINO SOBRINHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35295-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Mantena</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35243-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4965</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5.102
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17,73
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3115474</x:t>
+  </x:si>
+  <x:si>
+    <x:t>catutiense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DELERMANDO DO NASCIMENTO FRANÇA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>39526-700</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Catuti</x:t>
+  </x:si>
+  <x:si>
+    <x:t>72018</x:t>
+  </x:si>
+  <x:si>
+    <x:t>66.803
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30,63
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3135100</x:t>
+  </x:si>
+  <x:si>
+    <x:t>janaubense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JOSÉ APARECIDO MENDES SANTOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>39449-300</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Janaúba</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35952-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35422-500</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15890</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.024
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,87
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3127800</x:t>
+  </x:si>
+  <x:si>
+    <x:t>grão-mogolense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DIÊGO ANTONIO BRAGA FAGUNDES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>39572-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Grão Mogol</x:t>
+  </x:si>
+  <x:si>
+    <x:t>32866</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28.442
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>83,51
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3105400</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cocaiense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>DÉCIO GERALDO DOS SANTOS</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35970-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Barão de Cocais</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35459-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3491</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3.516
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5,53
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3124708</x:t>
+  </x:si>
+  <x:si>
+    <x:t>estrelense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WESLEY DANIEL RIBEIRO ARAUJO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35615-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Estrela do Indaiá</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10262</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.004
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>91,66
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3106002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bela-vistano</x:t>
+  </x:si>
+  <x:si>
+    <x:t>SAMANTHA APARECIDA DE ÁVILA COSTA MAGALHÃES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35938-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bela Vista de Minas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3425</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3.403
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8,66
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3106101</x:t>
+  </x:si>
+  <x:si>
+    <x:t>belmirense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JOSÉ PAULO DE OLIVEIRA FRANCO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>36126-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Belmiro Braga</x:t>
+  </x:si>
+  <x:si>
+    <x:t>26994</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23.397
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>69,86
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3106309</x:t>
+  </x:si>
+  <x:si>
+    <x:t>belo-orientino</x:t>
+  </x:si>
+  <x:si>
+    <x:t>HAMILTON ROMULO DE MENEZES CARVALHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35195-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Belo Oriente</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7719</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7.536
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20,59
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3106408</x:t>
+  </x:si>
+  <x:si>
+    <x:t>belo-valense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>WALTENIR LIBERATO SOARES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35473-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Belo Vale</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11872</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12.300
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20,95
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3106507</x:t>
+  </x:si>
+  <x:si>
+    <x:t>berilense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ELANE LUIZ ALVES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>39640-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Berilo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4764</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4.370
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8,94
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3106655</x:t>
+  </x:si>
+  <x:si>
+    <x:t>berizalense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JOÃO CARLOS LUCAS LOPES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>39555-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Berizal</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23711</x:t>
+  </x:si>
+  <x:si>
+    <x:t>23.818
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31,20
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3154002</x:t>
+  </x:si>
+  <x:si>
+    <x:t>raul-soarense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>AMÉRICO DE ALMEIDA CÉZAR</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35352-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Raul Soares</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2498</x:t>
+  </x:si>
+  <x:si>
+    <x:t>2.630
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5,73
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3107000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>biquinhense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ARISLEU FERREIRA PIRES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35621-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Biquinhas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4852</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5.395
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22,84
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3135407</x:t>
+  </x:si>
+  <x:si>
+    <x:t>jeceabense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JOSE DONIZETE ALMEIDA MAIA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35497-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Jeceaba</x:t>
+  </x:si>
+  <x:si>
+    <x:t>38208-700</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35579-600</x:t>
+  </x:si>
+  <x:si>
+    <x:t>11576</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.692
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>51,16
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3131802</x:t>
+  </x:si>
+  <x:si>
+    <x:t>itabirense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>LUCAS COIMBRA DONADIA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35285-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Itabirinha</x:t>
+  </x:si>
+  <x:si>
+    <x:t>32812-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>105520</x:t>
+  </x:si>
+  <x:si>
+    <x:t>73.699
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>261,00
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3145208</x:t>
+  </x:si>
+  <x:si>
+    <x:t>nova-serranense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EUZEBIO RODRIGUES LAGO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35529-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Nova Serrana</x:t>
+  </x:si>
+  <x:si>
+    <x:t>84930</x:t>
+  </x:si>
+  <x:si>
+    <x:t>77.565
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9,18
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3170404</x:t>
+  </x:si>
+  <x:si>
+    <x:t>unaiense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JOSE GOMES BRANQUINHO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>38621-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Unaí</x:t>
+  </x:si>
+  <x:si>
+    <x:t>51028</x:t>
+  </x:si>
+  <x:si>
+    <x:t>45.624
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>37,28
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3107406</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bom-despachense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>BERTOLINO DA COSTA NETO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35600-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bom Despacho</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19559</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17.048
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>42,62
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3114501</x:t>
+  </x:si>
+  <x:si>
+    <x:t>carmopolitano</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JOSÉ OMAR PAOLINELLI</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35535-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Carmópolis de Minas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4244</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3.887
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18,66
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3107604</x:t>
+  </x:si>
+  <x:si>
+    <x:t>bom-jesuense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>NEI ANDRÉ FREIRE</x:t>
+  </x:si>
+  <x:si>
+    <x:t>37948-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bom Jesus da Penha</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22693</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20.012
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43,90
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3114204</x:t>
+  </x:si>
+  <x:si>
+    <x:t>cajuruense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>EDSON DE SOUZA VILELA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35559-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Carmo do Cajuru</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10345</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10.291
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>74,15
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3170503</x:t>
+  </x:si>
+  <x:si>
+    <x:t>urucaniense</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JOSÉ MÁRCIO GOMES OSÓRIO</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35381-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Urucânia</x:t>
+  </x:si>
+  <x:si>
+    <x:t>6133</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5.491
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28,07
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3107703</x:t>
+  </x:si>
+  <x:si>
+    <x:t>PEDRO DOS SANTOS MOREIRA</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35908-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bom Jesus do Amparo</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14862</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15.364
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25,94
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3107802</x:t>
+  </x:si>
+  <x:si>
+    <x:t>ANIBAL BORGES</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35340-000</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Bom Jesus do Galho</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9664</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8.920
+    pessoas</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19,00
+    hab/km²</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3126901</x:t>
+  </x:si>
+  <x:si>
+    <x:t>frei-inocenciano</x:t>
+  </x:si>
+  <x:si>
+    <x:t>JIMMY DUTRA GOULART</x:t>
+  </x:si>
+  <x:si>
+    <x:t>35112-800</x:t>
+  </x:si>
+  <x:si>
+    <x:t>Frei Inocêncio</x:t>
   </x:si>
 </x:sst>
 </file>
@@ -405,10 +2649,10 @@
   <x:sheetPr>
     <x:outlinePr summaryBelow="1" summaryRight="1"/>
   </x:sheetPr>
-  <x:dimension ref="A1:G58"/>
+  <x:dimension ref="A1:I100"/>
   <x:sheetFormatPr defaultRowHeight="15"/>
   <x:sheetData>
-    <x:row r="1" spans="1:7">
+    <x:row r="1" spans="1:9">
       <x:c r="A1" s="0" t="s">
         <x:v>0</x:v>
       </x:c>
@@ -430,1145 +2674,2882 @@
       <x:c r="G1" s="0" t="s">
         <x:v>6</x:v>
       </x:c>
-    </x:row>
-    <x:row r="2" spans="1:7">
+      <x:c r="H1" s="0" t="s">
+        <x:v>7</x:v>
+      </x:c>
+      <x:c r="I1" s="0" t="s">
+        <x:v>8</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="2" spans="1:9">
       <x:c r="A2" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>9</x:v>
       </x:c>
       <x:c r="B2" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>10</x:v>
       </x:c>
       <x:c r="C2" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>11</x:v>
       </x:c>
       <x:c r="D2" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>12</x:v>
       </x:c>
       <x:c r="E2" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>13</x:v>
       </x:c>
       <x:c r="F2" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="3" spans="1:7">
+        <x:v>14</x:v>
+      </x:c>
+      <x:c r="G2" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H2" s="0" t="s">
+        <x:v>16</x:v>
+      </x:c>
+      <x:c r="I2" s="0" t="s">
+        <x:v>17</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="3" spans="1:9">
       <x:c r="A3" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>18</x:v>
       </x:c>
       <x:c r="B3" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>19</x:v>
       </x:c>
       <x:c r="C3" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>20</x:v>
       </x:c>
       <x:c r="D3" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>21</x:v>
       </x:c>
       <x:c r="E3" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>22</x:v>
       </x:c>
       <x:c r="F3" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="4" spans="1:7">
+        <x:v>23</x:v>
+      </x:c>
+      <x:c r="G3" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H3" s="0" t="s">
+        <x:v>25</x:v>
+      </x:c>
+      <x:c r="I3" s="0" t="s">
+        <x:v>26</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="4" spans="1:9">
       <x:c r="A4" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>27</x:v>
       </x:c>
       <x:c r="B4" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>28</x:v>
       </x:c>
       <x:c r="C4" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>29</x:v>
       </x:c>
       <x:c r="D4" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>30</x:v>
       </x:c>
       <x:c r="E4" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>31</x:v>
       </x:c>
       <x:c r="F4" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="5" spans="1:7">
+        <x:v>32</x:v>
+      </x:c>
+      <x:c r="G4" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H4" s="0" t="s">
+        <x:v>33</x:v>
+      </x:c>
+      <x:c r="I4" s="0" t="s">
+        <x:v>34</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="5" spans="1:9">
       <x:c r="A5" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>35</x:v>
       </x:c>
       <x:c r="B5" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>36</x:v>
       </x:c>
       <x:c r="C5" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>37</x:v>
       </x:c>
       <x:c r="D5" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>38</x:v>
       </x:c>
       <x:c r="E5" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>39</x:v>
       </x:c>
       <x:c r="F5" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="6" spans="1:7">
+        <x:v>40</x:v>
+      </x:c>
+      <x:c r="G5" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H5" s="0" t="s">
+        <x:v>41</x:v>
+      </x:c>
+      <x:c r="I5" s="0" t="s">
+        <x:v>42</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="6" spans="1:9">
       <x:c r="A6" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>43</x:v>
       </x:c>
       <x:c r="B6" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>44</x:v>
       </x:c>
       <x:c r="C6" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>45</x:v>
       </x:c>
       <x:c r="D6" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>46</x:v>
       </x:c>
       <x:c r="E6" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>47</x:v>
       </x:c>
       <x:c r="F6" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="7" spans="1:7">
+        <x:v>48</x:v>
+      </x:c>
+      <x:c r="G6" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H6" s="0" t="s">
+        <x:v>49</x:v>
+      </x:c>
+      <x:c r="I6" s="0" t="s">
+        <x:v>50</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="7" spans="1:9">
       <x:c r="A7" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>51</x:v>
       </x:c>
       <x:c r="B7" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>52</x:v>
       </x:c>
       <x:c r="C7" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>53</x:v>
       </x:c>
       <x:c r="D7" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>54</x:v>
       </x:c>
       <x:c r="E7" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>55</x:v>
       </x:c>
       <x:c r="F7" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="8" spans="1:7">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="G7" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H7" s="0" t="s">
+        <x:v>58</x:v>
+      </x:c>
+      <x:c r="I7" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="8" spans="1:9">
       <x:c r="A8" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>60</x:v>
       </x:c>
       <x:c r="B8" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>61</x:v>
       </x:c>
       <x:c r="C8" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>62</x:v>
       </x:c>
       <x:c r="D8" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>63</x:v>
       </x:c>
       <x:c r="E8" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>64</x:v>
       </x:c>
       <x:c r="F8" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="9" spans="1:7">
+        <x:v>65</x:v>
+      </x:c>
+      <x:c r="G8" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H8" s="0" t="s">
+        <x:v>66</x:v>
+      </x:c>
+      <x:c r="I8" s="0" t="s">
+        <x:v>67</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="9" spans="1:9">
       <x:c r="A9" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B9" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C9" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D9" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E9" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F9" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="10" spans="1:7">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="G9" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H9" s="0" t="s">
+        <x:v>74</x:v>
+      </x:c>
+      <x:c r="I9" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="10" spans="1:9">
       <x:c r="A10" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>76</x:v>
       </x:c>
       <x:c r="B10" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>77</x:v>
       </x:c>
       <x:c r="C10" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>78</x:v>
       </x:c>
       <x:c r="D10" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>79</x:v>
       </x:c>
       <x:c r="E10" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>80</x:v>
       </x:c>
       <x:c r="F10" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="11" spans="1:7">
+        <x:v>81</x:v>
+      </x:c>
+      <x:c r="G10" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H10" s="0" t="s">
+        <x:v>82</x:v>
+      </x:c>
+      <x:c r="I10" s="0" t="s">
+        <x:v>83</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="11" spans="1:9">
       <x:c r="A11" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>84</x:v>
       </x:c>
       <x:c r="B11" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>85</x:v>
       </x:c>
       <x:c r="C11" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>86</x:v>
       </x:c>
       <x:c r="D11" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>87</x:v>
       </x:c>
       <x:c r="E11" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>88</x:v>
       </x:c>
       <x:c r="F11" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="12" spans="1:7">
+        <x:v>89</x:v>
+      </x:c>
+      <x:c r="G11" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H11" s="0" t="s">
+        <x:v>90</x:v>
+      </x:c>
+      <x:c r="I11" s="0" t="s">
+        <x:v>91</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="12" spans="1:9">
       <x:c r="A12" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>92</x:v>
       </x:c>
       <x:c r="B12" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>93</x:v>
       </x:c>
       <x:c r="C12" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>94</x:v>
       </x:c>
       <x:c r="D12" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>95</x:v>
       </x:c>
       <x:c r="E12" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>96</x:v>
       </x:c>
       <x:c r="F12" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="13" spans="1:7">
+        <x:v>97</x:v>
+      </x:c>
+      <x:c r="G12" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H12" s="0" t="s">
+        <x:v>98</x:v>
+      </x:c>
+      <x:c r="I12" s="0" t="s">
+        <x:v>99</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="13" spans="1:9">
       <x:c r="A13" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>100</x:v>
       </x:c>
       <x:c r="B13" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>101</x:v>
       </x:c>
       <x:c r="C13" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>102</x:v>
       </x:c>
       <x:c r="D13" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>103</x:v>
       </x:c>
       <x:c r="E13" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>104</x:v>
       </x:c>
       <x:c r="F13" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="14" spans="1:7">
+        <x:v>105</x:v>
+      </x:c>
+      <x:c r="G13" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H13" s="0" t="s">
+        <x:v>106</x:v>
+      </x:c>
+      <x:c r="I13" s="0" t="s">
+        <x:v>107</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="14" spans="1:9">
       <x:c r="A14" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>108</x:v>
       </x:c>
       <x:c r="B14" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>109</x:v>
       </x:c>
       <x:c r="C14" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>110</x:v>
       </x:c>
       <x:c r="D14" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>111</x:v>
       </x:c>
       <x:c r="E14" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>112</x:v>
       </x:c>
       <x:c r="F14" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="15" spans="1:7">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="G14" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H14" s="0" t="s">
+        <x:v>114</x:v>
+      </x:c>
+      <x:c r="I14" s="0" t="s">
+        <x:v>115</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="15" spans="1:9">
       <x:c r="A15" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>116</x:v>
       </x:c>
       <x:c r="B15" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>117</x:v>
       </x:c>
       <x:c r="C15" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>118</x:v>
       </x:c>
       <x:c r="D15" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>119</x:v>
       </x:c>
       <x:c r="E15" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>120</x:v>
       </x:c>
       <x:c r="F15" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="16" spans="1:7">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="G15" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H15" s="0" t="s">
+        <x:v>122</x:v>
+      </x:c>
+      <x:c r="I15" s="0" t="s">
+        <x:v>123</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="16" spans="1:9">
       <x:c r="A16" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>124</x:v>
       </x:c>
       <x:c r="B16" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>125</x:v>
       </x:c>
       <x:c r="C16" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>126</x:v>
       </x:c>
       <x:c r="D16" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>127</x:v>
       </x:c>
       <x:c r="E16" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>128</x:v>
       </x:c>
       <x:c r="F16" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="17" spans="1:7">
+        <x:v>129</x:v>
+      </x:c>
+      <x:c r="G16" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H16" s="0" t="s">
+        <x:v>130</x:v>
+      </x:c>
+      <x:c r="I16" s="0" t="s">
+        <x:v>131</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="17" spans="1:9">
       <x:c r="A17" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>132</x:v>
       </x:c>
       <x:c r="B17" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>133</x:v>
       </x:c>
       <x:c r="C17" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>134</x:v>
       </x:c>
       <x:c r="D17" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>135</x:v>
       </x:c>
       <x:c r="E17" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>136</x:v>
       </x:c>
       <x:c r="F17" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="18" spans="1:7">
+        <x:v>137</x:v>
+      </x:c>
+      <x:c r="G17" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H17" s="0" t="s">
+        <x:v>138</x:v>
+      </x:c>
+      <x:c r="I17" s="0" t="s">
+        <x:v>139</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="18" spans="1:9">
       <x:c r="A18" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>140</x:v>
       </x:c>
       <x:c r="B18" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>141</x:v>
       </x:c>
       <x:c r="C18" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>142</x:v>
       </x:c>
       <x:c r="D18" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>143</x:v>
       </x:c>
       <x:c r="E18" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>144</x:v>
       </x:c>
       <x:c r="F18" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="19" spans="1:7">
+        <x:v>145</x:v>
+      </x:c>
+      <x:c r="G18" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H18" s="0" t="s">
+        <x:v>146</x:v>
+      </x:c>
+      <x:c r="I18" s="0" t="s">
+        <x:v>147</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="19" spans="1:9">
       <x:c r="A19" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>148</x:v>
       </x:c>
       <x:c r="B19" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>149</x:v>
       </x:c>
       <x:c r="C19" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>150</x:v>
       </x:c>
       <x:c r="D19" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>151</x:v>
       </x:c>
       <x:c r="E19" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>152</x:v>
       </x:c>
       <x:c r="F19" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="20" spans="1:7">
+        <x:v>153</x:v>
+      </x:c>
+      <x:c r="G19" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H19" s="0" t="s">
+        <x:v>154</x:v>
+      </x:c>
+      <x:c r="I19" s="0" t="s">
+        <x:v>155</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="20" spans="1:9">
       <x:c r="A20" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>156</x:v>
       </x:c>
       <x:c r="B20" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>157</x:v>
       </x:c>
       <x:c r="C20" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>158</x:v>
       </x:c>
       <x:c r="D20" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>159</x:v>
       </x:c>
       <x:c r="E20" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>160</x:v>
       </x:c>
       <x:c r="F20" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="21" spans="1:7">
+        <x:v>161</x:v>
+      </x:c>
+      <x:c r="G20" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H20" s="0" t="s">
+        <x:v>162</x:v>
+      </x:c>
+      <x:c r="I20" s="0" t="s">
+        <x:v>163</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="21" spans="1:9">
       <x:c r="A21" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>68</x:v>
       </x:c>
       <x:c r="B21" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>69</x:v>
       </x:c>
       <x:c r="C21" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>70</x:v>
       </x:c>
       <x:c r="D21" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>71</x:v>
       </x:c>
       <x:c r="E21" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>72</x:v>
       </x:c>
       <x:c r="F21" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="22" spans="1:7">
+        <x:v>73</x:v>
+      </x:c>
+      <x:c r="G21" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H21" s="0" t="s">
+        <x:v>164</x:v>
+      </x:c>
+      <x:c r="I21" s="0" t="s">
+        <x:v>75</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="22" spans="1:9">
       <x:c r="A22" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="B22" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="C22" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="D22" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="E22" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="F22" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="23" spans="1:7">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="G22" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H22" s="0" t="s">
+        <x:v>171</x:v>
+      </x:c>
+      <x:c r="I22" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="23" spans="1:9">
       <x:c r="A23" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>173</x:v>
       </x:c>
       <x:c r="B23" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>174</x:v>
       </x:c>
       <x:c r="C23" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>175</x:v>
       </x:c>
       <x:c r="D23" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>176</x:v>
       </x:c>
       <x:c r="E23" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>177</x:v>
       </x:c>
       <x:c r="F23" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="24" spans="1:7">
+        <x:v>178</x:v>
+      </x:c>
+      <x:c r="G23" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H23" s="0" t="s">
+        <x:v>179</x:v>
+      </x:c>
+      <x:c r="I23" s="0" t="s">
+        <x:v>180</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="24" spans="1:9">
       <x:c r="A24" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>181</x:v>
       </x:c>
       <x:c r="B24" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>182</x:v>
       </x:c>
       <x:c r="C24" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>183</x:v>
       </x:c>
       <x:c r="D24" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>184</x:v>
       </x:c>
       <x:c r="E24" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>185</x:v>
       </x:c>
       <x:c r="F24" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="25" spans="1:7">
+        <x:v>186</x:v>
+      </x:c>
+      <x:c r="G24" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H24" s="0" t="s">
+        <x:v>187</x:v>
+      </x:c>
+      <x:c r="I24" s="0" t="s">
+        <x:v>188</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="25" spans="1:9">
       <x:c r="A25" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>189</x:v>
       </x:c>
       <x:c r="B25" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>190</x:v>
       </x:c>
       <x:c r="C25" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>191</x:v>
       </x:c>
       <x:c r="D25" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>192</x:v>
       </x:c>
       <x:c r="E25" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>193</x:v>
       </x:c>
       <x:c r="F25" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="26" spans="1:7">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="G25" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H25" s="0" t="s">
+        <x:v>195</x:v>
+      </x:c>
+      <x:c r="I25" s="0" t="s">
+        <x:v>196</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="26" spans="1:9">
       <x:c r="A26" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="B26" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="C26" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="D26" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="E26" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="F26" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="27" spans="1:7">
+        <x:v>202</x:v>
+      </x:c>
+      <x:c r="G26" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H26" s="0" t="s">
+        <x:v>203</x:v>
+      </x:c>
+      <x:c r="I26" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="27" spans="1:9">
       <x:c r="A27" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>205</x:v>
       </x:c>
       <x:c r="B27" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>206</x:v>
       </x:c>
       <x:c r="C27" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>207</x:v>
       </x:c>
       <x:c r="D27" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>208</x:v>
       </x:c>
       <x:c r="E27" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>209</x:v>
       </x:c>
       <x:c r="F27" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="28" spans="1:7">
+        <x:v>210</x:v>
+      </x:c>
+      <x:c r="G27" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H27" s="0" t="s">
+        <x:v>211</x:v>
+      </x:c>
+      <x:c r="I27" s="0" t="s">
+        <x:v>212</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="28" spans="1:9">
       <x:c r="A28" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="B28" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="C28" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="D28" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="E28" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="F28" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="29" spans="1:7">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="G28" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H28" s="0" t="s">
+        <x:v>219</x:v>
+      </x:c>
+      <x:c r="I28" s="0" t="s">
+        <x:v>220</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="29" spans="1:9">
       <x:c r="A29" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>221</x:v>
       </x:c>
       <x:c r="B29" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>222</x:v>
       </x:c>
       <x:c r="C29" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>223</x:v>
       </x:c>
       <x:c r="D29" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>224</x:v>
       </x:c>
       <x:c r="E29" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>225</x:v>
       </x:c>
       <x:c r="F29" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="30" spans="1:7">
+        <x:v>226</x:v>
+      </x:c>
+      <x:c r="G29" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H29" s="0" t="s">
+        <x:v>227</x:v>
+      </x:c>
+      <x:c r="I29" s="0" t="s">
+        <x:v>228</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="30" spans="1:9">
       <x:c r="A30" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>229</x:v>
       </x:c>
       <x:c r="B30" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>230</x:v>
       </x:c>
       <x:c r="C30" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>231</x:v>
       </x:c>
       <x:c r="D30" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>232</x:v>
       </x:c>
       <x:c r="E30" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>233</x:v>
       </x:c>
       <x:c r="F30" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="31" spans="1:7">
+        <x:v>234</x:v>
+      </x:c>
+      <x:c r="G30" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H30" s="0" t="s">
+        <x:v>235</x:v>
+      </x:c>
+      <x:c r="I30" s="0" t="s">
+        <x:v>236</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="31" spans="1:9">
       <x:c r="A31" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>237</x:v>
       </x:c>
       <x:c r="B31" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>238</x:v>
       </x:c>
       <x:c r="C31" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>239</x:v>
       </x:c>
       <x:c r="D31" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>240</x:v>
       </x:c>
       <x:c r="E31" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>241</x:v>
       </x:c>
       <x:c r="F31" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="32" spans="1:7">
+        <x:v>242</x:v>
+      </x:c>
+      <x:c r="G31" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H31" s="0" t="s">
+        <x:v>243</x:v>
+      </x:c>
+      <x:c r="I31" s="0" t="s">
+        <x:v>244</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="32" spans="1:9">
       <x:c r="A32" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>245</x:v>
       </x:c>
       <x:c r="B32" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>246</x:v>
       </x:c>
       <x:c r="C32" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>247</x:v>
       </x:c>
       <x:c r="D32" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>248</x:v>
       </x:c>
       <x:c r="E32" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>249</x:v>
       </x:c>
       <x:c r="F32" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="33" spans="1:7">
+        <x:v>250</x:v>
+      </x:c>
+      <x:c r="G32" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H32" s="0" t="s">
+        <x:v>251</x:v>
+      </x:c>
+      <x:c r="I32" s="0" t="s">
+        <x:v>252</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="33" spans="1:9">
       <x:c r="A33" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>253</x:v>
       </x:c>
       <x:c r="B33" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>254</x:v>
       </x:c>
       <x:c r="C33" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>255</x:v>
       </x:c>
       <x:c r="D33" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>256</x:v>
       </x:c>
       <x:c r="E33" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>257</x:v>
       </x:c>
       <x:c r="F33" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="34" spans="1:7">
+        <x:v>258</x:v>
+      </x:c>
+      <x:c r="G33" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H33" s="0" t="s">
+        <x:v>259</x:v>
+      </x:c>
+      <x:c r="I33" s="0" t="s">
+        <x:v>260</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="34" spans="1:9">
       <x:c r="A34" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>261</x:v>
       </x:c>
       <x:c r="B34" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>262</x:v>
       </x:c>
       <x:c r="C34" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>263</x:v>
       </x:c>
       <x:c r="D34" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>264</x:v>
       </x:c>
       <x:c r="E34" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>265</x:v>
       </x:c>
       <x:c r="F34" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="35" spans="1:7">
+        <x:v>266</x:v>
+      </x:c>
+      <x:c r="G34" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H34" s="0" t="s">
+        <x:v>267</x:v>
+      </x:c>
+      <x:c r="I34" s="0" t="s">
+        <x:v>268</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="35" spans="1:9">
       <x:c r="A35" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>213</x:v>
       </x:c>
       <x:c r="B35" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>214</x:v>
       </x:c>
       <x:c r="C35" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>215</x:v>
       </x:c>
       <x:c r="D35" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>216</x:v>
       </x:c>
       <x:c r="E35" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>217</x:v>
       </x:c>
       <x:c r="F35" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="36" spans="1:7">
+        <x:v>218</x:v>
+      </x:c>
+      <x:c r="G35" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H35" s="0" t="s">
+        <x:v>269</x:v>
+      </x:c>
+      <x:c r="I35" s="0" t="s">
+        <x:v>220</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="36" spans="1:9">
       <x:c r="A36" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>270</x:v>
       </x:c>
       <x:c r="B36" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>271</x:v>
       </x:c>
       <x:c r="C36" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>272</x:v>
       </x:c>
       <x:c r="D36" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>273</x:v>
       </x:c>
       <x:c r="E36" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>274</x:v>
       </x:c>
       <x:c r="F36" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="37" spans="1:7">
+        <x:v>275</x:v>
+      </x:c>
+      <x:c r="G36" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H36" s="0" t="s">
+        <x:v>276</x:v>
+      </x:c>
+      <x:c r="I36" s="0" t="s">
+        <x:v>277</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="37" spans="1:9">
       <x:c r="A37" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>278</x:v>
       </x:c>
       <x:c r="B37" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>279</x:v>
       </x:c>
       <x:c r="C37" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>280</x:v>
       </x:c>
       <x:c r="D37" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>281</x:v>
       </x:c>
       <x:c r="E37" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>282</x:v>
       </x:c>
       <x:c r="F37" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="38" spans="1:7">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="G37" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H37" s="0" t="s">
+        <x:v>284</x:v>
+      </x:c>
+      <x:c r="I37" s="0" t="s">
+        <x:v>285</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="38" spans="1:9">
       <x:c r="A38" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="B38" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="C38" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="D38" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="E38" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="F38" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="39" spans="1:7">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="G38" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H38" s="0" t="s">
+        <x:v>292</x:v>
+      </x:c>
+      <x:c r="I38" s="0" t="s">
+        <x:v>293</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="39" spans="1:9">
       <x:c r="A39" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>294</x:v>
       </x:c>
       <x:c r="B39" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>295</x:v>
       </x:c>
       <x:c r="C39" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>296</x:v>
       </x:c>
       <x:c r="D39" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>297</x:v>
       </x:c>
       <x:c r="E39" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>298</x:v>
       </x:c>
       <x:c r="F39" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="40" spans="1:7">
+        <x:v>299</x:v>
+      </x:c>
+      <x:c r="G39" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H39" s="0" t="s">
+        <x:v>300</x:v>
+      </x:c>
+      <x:c r="I39" s="0" t="s">
+        <x:v>301</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="40" spans="1:9">
       <x:c r="A40" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>302</x:v>
       </x:c>
       <x:c r="B40" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>303</x:v>
       </x:c>
       <x:c r="C40" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>304</x:v>
       </x:c>
       <x:c r="D40" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>305</x:v>
       </x:c>
       <x:c r="E40" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>306</x:v>
       </x:c>
       <x:c r="F40" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="41" spans="1:7">
+        <x:v>307</x:v>
+      </x:c>
+      <x:c r="G40" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H40" s="0" t="s">
+        <x:v>308</x:v>
+      </x:c>
+      <x:c r="I40" s="0" t="s">
+        <x:v>309</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="41" spans="1:9">
       <x:c r="A41" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>310</x:v>
       </x:c>
       <x:c r="B41" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>311</x:v>
       </x:c>
       <x:c r="C41" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>312</x:v>
       </x:c>
       <x:c r="D41" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>313</x:v>
       </x:c>
       <x:c r="E41" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>314</x:v>
       </x:c>
       <x:c r="F41" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="42" spans="1:7">
+        <x:v>315</x:v>
+      </x:c>
+      <x:c r="G41" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H41" s="0" t="s">
+        <x:v>316</x:v>
+      </x:c>
+      <x:c r="I41" s="0" t="s">
+        <x:v>317</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="42" spans="1:9">
       <x:c r="A42" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>318</x:v>
       </x:c>
       <x:c r="B42" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>319</x:v>
       </x:c>
       <x:c r="C42" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>320</x:v>
       </x:c>
       <x:c r="D42" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>321</x:v>
       </x:c>
       <x:c r="E42" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>322</x:v>
       </x:c>
       <x:c r="F42" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="43" spans="1:7">
+        <x:v>323</x:v>
+      </x:c>
+      <x:c r="G42" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H42" s="0" t="s">
+        <x:v>324</x:v>
+      </x:c>
+      <x:c r="I42" s="0" t="s">
+        <x:v>325</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="43" spans="1:9">
       <x:c r="A43" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>326</x:v>
       </x:c>
       <x:c r="B43" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>327</x:v>
       </x:c>
       <x:c r="C43" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>328</x:v>
       </x:c>
       <x:c r="D43" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>329</x:v>
       </x:c>
       <x:c r="E43" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>330</x:v>
       </x:c>
       <x:c r="F43" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="44" spans="1:7">
+        <x:v>331</x:v>
+      </x:c>
+      <x:c r="G43" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H43" s="0" t="s">
+        <x:v>332</x:v>
+      </x:c>
+      <x:c r="I43" s="0" t="s">
+        <x:v>333</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="44" spans="1:9">
       <x:c r="A44" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>334</x:v>
       </x:c>
       <x:c r="B44" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>335</x:v>
       </x:c>
       <x:c r="C44" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>336</x:v>
       </x:c>
       <x:c r="D44" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>337</x:v>
       </x:c>
       <x:c r="E44" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>338</x:v>
       </x:c>
       <x:c r="F44" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="45" spans="1:7">
+        <x:v>339</x:v>
+      </x:c>
+      <x:c r="G44" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H44" s="0" t="s">
+        <x:v>340</x:v>
+      </x:c>
+      <x:c r="I44" s="0" t="s">
+        <x:v>341</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="45" spans="1:9">
       <x:c r="A45" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>342</x:v>
       </x:c>
       <x:c r="B45" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>343</x:v>
       </x:c>
       <x:c r="C45" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>344</x:v>
       </x:c>
       <x:c r="D45" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>345</x:v>
       </x:c>
       <x:c r="E45" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>346</x:v>
       </x:c>
       <x:c r="F45" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="46" spans="1:7">
+        <x:v>347</x:v>
+      </x:c>
+      <x:c r="G45" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H45" s="0" t="s">
+        <x:v>348</x:v>
+      </x:c>
+      <x:c r="I45" s="0" t="s">
+        <x:v>349</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="46" spans="1:9">
       <x:c r="A46" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>350</x:v>
       </x:c>
       <x:c r="B46" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>351</x:v>
       </x:c>
       <x:c r="C46" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>352</x:v>
       </x:c>
       <x:c r="D46" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>353</x:v>
       </x:c>
       <x:c r="E46" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>354</x:v>
       </x:c>
       <x:c r="F46" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="47" spans="1:7">
+        <x:v>355</x:v>
+      </x:c>
+      <x:c r="G46" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H46" s="0" t="s">
+        <x:v>356</x:v>
+      </x:c>
+      <x:c r="I46" s="0" t="s">
+        <x:v>357</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="47" spans="1:9">
       <x:c r="A47" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>358</x:v>
       </x:c>
       <x:c r="B47" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>359</x:v>
       </x:c>
       <x:c r="C47" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>360</x:v>
       </x:c>
       <x:c r="D47" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>361</x:v>
       </x:c>
       <x:c r="E47" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>362</x:v>
       </x:c>
       <x:c r="F47" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="48" spans="1:7">
+        <x:v>363</x:v>
+      </x:c>
+      <x:c r="G47" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H47" s="0" t="s">
+        <x:v>364</x:v>
+      </x:c>
+      <x:c r="I47" s="0" t="s">
+        <x:v>365</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="48" spans="1:9">
       <x:c r="A48" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>366</x:v>
       </x:c>
       <x:c r="B48" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>367</x:v>
       </x:c>
       <x:c r="C48" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>368</x:v>
       </x:c>
       <x:c r="D48" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>369</x:v>
       </x:c>
       <x:c r="E48" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>370</x:v>
       </x:c>
       <x:c r="F48" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="49" spans="1:7">
+        <x:v>371</x:v>
+      </x:c>
+      <x:c r="G48" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H48" s="0" t="s">
+        <x:v>372</x:v>
+      </x:c>
+      <x:c r="I48" s="0" t="s">
+        <x:v>373</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="49" spans="1:9">
       <x:c r="A49" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>374</x:v>
       </x:c>
       <x:c r="B49" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>375</x:v>
       </x:c>
       <x:c r="C49" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>376</x:v>
       </x:c>
       <x:c r="D49" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>377</x:v>
       </x:c>
       <x:c r="E49" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>378</x:v>
       </x:c>
       <x:c r="F49" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="50" spans="1:7">
+        <x:v>379</x:v>
+      </x:c>
+      <x:c r="G49" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H49" s="0" t="s">
+        <x:v>380</x:v>
+      </x:c>
+      <x:c r="I49" s="0" t="s">
+        <x:v>381</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="50" spans="1:9">
       <x:c r="A50" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>382</x:v>
       </x:c>
       <x:c r="B50" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>383</x:v>
       </x:c>
       <x:c r="C50" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>384</x:v>
       </x:c>
       <x:c r="D50" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>385</x:v>
       </x:c>
       <x:c r="E50" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>386</x:v>
       </x:c>
       <x:c r="F50" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="51" spans="1:7">
+        <x:v>387</x:v>
+      </x:c>
+      <x:c r="G50" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H50" s="0" t="s">
+        <x:v>388</x:v>
+      </x:c>
+      <x:c r="I50" s="0" t="s">
+        <x:v>389</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="51" spans="1:9">
       <x:c r="A51" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>390</x:v>
       </x:c>
       <x:c r="B51" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>391</x:v>
       </x:c>
       <x:c r="C51" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>392</x:v>
       </x:c>
       <x:c r="D51" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>393</x:v>
       </x:c>
       <x:c r="E51" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>394</x:v>
       </x:c>
       <x:c r="F51" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="52" spans="1:7">
+        <x:v>395</x:v>
+      </x:c>
+      <x:c r="G51" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H51" s="0" t="s">
+        <x:v>396</x:v>
+      </x:c>
+      <x:c r="I51" s="0" t="s">
+        <x:v>397</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="52" spans="1:9">
       <x:c r="A52" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>398</x:v>
       </x:c>
       <x:c r="B52" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>399</x:v>
       </x:c>
       <x:c r="C52" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>400</x:v>
       </x:c>
       <x:c r="D52" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>401</x:v>
       </x:c>
       <x:c r="E52" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>402</x:v>
       </x:c>
       <x:c r="F52" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="53" spans="1:7">
+        <x:v>403</x:v>
+      </x:c>
+      <x:c r="G52" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H52" s="0" t="s">
+        <x:v>404</x:v>
+      </x:c>
+      <x:c r="I52" s="0" t="s">
+        <x:v>405</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="53" spans="1:9">
       <x:c r="A53" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>286</x:v>
       </x:c>
       <x:c r="B53" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>287</x:v>
       </x:c>
       <x:c r="C53" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>288</x:v>
       </x:c>
       <x:c r="D53" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>289</x:v>
       </x:c>
       <x:c r="E53" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>290</x:v>
       </x:c>
       <x:c r="F53" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="54" spans="1:7">
+        <x:v>291</x:v>
+      </x:c>
+      <x:c r="G53" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H53" s="0" t="s">
+        <x:v>406</x:v>
+      </x:c>
+      <x:c r="I53" s="0" t="s">
+        <x:v>293</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="54" spans="1:9">
       <x:c r="A54" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>407</x:v>
       </x:c>
       <x:c r="B54" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>408</x:v>
       </x:c>
       <x:c r="C54" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>409</x:v>
       </x:c>
       <x:c r="D54" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>410</x:v>
       </x:c>
       <x:c r="E54" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>411</x:v>
       </x:c>
       <x:c r="F54" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="55" spans="1:7">
+        <x:v>412</x:v>
+      </x:c>
+      <x:c r="G54" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H54" s="0" t="s">
+        <x:v>413</x:v>
+      </x:c>
+      <x:c r="I54" s="0" t="s">
+        <x:v>414</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="55" spans="1:9">
       <x:c r="A55" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>415</x:v>
       </x:c>
       <x:c r="B55" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>416</x:v>
       </x:c>
       <x:c r="C55" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>417</x:v>
       </x:c>
       <x:c r="D55" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>418</x:v>
       </x:c>
       <x:c r="E55" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>419</x:v>
       </x:c>
       <x:c r="F55" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="56" spans="1:7">
+        <x:v>420</x:v>
+      </x:c>
+      <x:c r="G55" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H55" s="0" t="s">
+        <x:v>421</x:v>
+      </x:c>
+      <x:c r="I55" s="0" t="s">
+        <x:v>422</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="56" spans="1:9">
       <x:c r="A56" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>165</x:v>
       </x:c>
       <x:c r="B56" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>166</x:v>
       </x:c>
       <x:c r="C56" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>167</x:v>
       </x:c>
       <x:c r="D56" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>168</x:v>
       </x:c>
       <x:c r="E56" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>169</x:v>
       </x:c>
       <x:c r="F56" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="57" spans="1:7">
+        <x:v>170</x:v>
+      </x:c>
+      <x:c r="G56" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H56" s="0" t="s">
+        <x:v>423</x:v>
+      </x:c>
+      <x:c r="I56" s="0" t="s">
+        <x:v>172</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="57" spans="1:9">
       <x:c r="A57" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="B57" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="C57" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="D57" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="E57" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="F57" s="0" t="s">
-        <x:v>12</x:v>
-      </x:c>
-    </x:row>
-    <x:row r="58" spans="1:7">
+        <x:v>429</x:v>
+      </x:c>
+      <x:c r="G57" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H57" s="0" t="s">
+        <x:v>430</x:v>
+      </x:c>
+      <x:c r="I57" s="0" t="s">
+        <x:v>431</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="58" spans="1:9">
       <x:c r="A58" s="0" t="s">
-        <x:v>7</x:v>
+        <x:v>424</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>8</x:v>
+        <x:v>425</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
-        <x:v>9</x:v>
+        <x:v>426</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
-        <x:v>10</x:v>
+        <x:v>427</x:v>
       </x:c>
       <x:c r="E58" s="0" t="s">
-        <x:v>11</x:v>
+        <x:v>428</x:v>
       </x:c>
       <x:c r="F58" s="0" t="s">
-        <x:v>12</x:v>
+        <x:v>429</x:v>
+      </x:c>
+      <x:c r="G58" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H58" s="0" t="s">
+        <x:v>432</x:v>
+      </x:c>
+      <x:c r="I58" s="0" t="s">
+        <x:v>433</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="59" spans="1:9">
+      <x:c r="A59" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="B59" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="C59" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="D59" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="E59" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="F59" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="G59" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H59" s="0" t="s">
+        <x:v>434</x:v>
+      </x:c>
+      <x:c r="I59" s="0" t="s">
+        <x:v>115</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="60" spans="1:9">
+      <x:c r="A60" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="B60" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="C60" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="D60" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="E60" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="F60" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="G60" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H60" s="0" t="s">
+        <x:v>435</x:v>
+      </x:c>
+      <x:c r="I60" s="0" t="s">
+        <x:v>204</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="61" spans="1:9">
+      <x:c r="A61" s="0" t="s">
+        <x:v>436</x:v>
+      </x:c>
+      <x:c r="B61" s="0" t="s">
+        <x:v>437</x:v>
+      </x:c>
+      <x:c r="C61" s="0" t="s">
+        <x:v>438</x:v>
+      </x:c>
+      <x:c r="D61" s="0" t="s">
+        <x:v>439</x:v>
+      </x:c>
+      <x:c r="E61" s="0" t="s">
+        <x:v>440</x:v>
+      </x:c>
+      <x:c r="F61" s="0" t="s">
+        <x:v>441</x:v>
+      </x:c>
+      <x:c r="G61" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H61" s="0" t="s">
+        <x:v>442</x:v>
+      </x:c>
+      <x:c r="I61" s="0" t="s">
+        <x:v>443</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="62" spans="1:9">
+      <x:c r="A62" s="0" t="s">
+        <x:v>444</x:v>
+      </x:c>
+      <x:c r="B62" s="0" t="s">
+        <x:v>445</x:v>
+      </x:c>
+      <x:c r="C62" s="0" t="s">
+        <x:v>446</x:v>
+      </x:c>
+      <x:c r="D62" s="0" t="s">
+        <x:v>447</x:v>
+      </x:c>
+      <x:c r="E62" s="0" t="s">
+        <x:v>448</x:v>
+      </x:c>
+      <x:c r="F62" s="0" t="s">
+        <x:v>449</x:v>
+      </x:c>
+      <x:c r="G62" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H62" s="0" t="s">
+        <x:v>450</x:v>
+      </x:c>
+      <x:c r="I62" s="0" t="s">
+        <x:v>451</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="63" spans="1:9">
+      <x:c r="A63" s="0" t="s">
+        <x:v>452</x:v>
+      </x:c>
+      <x:c r="B63" s="0" t="s">
+        <x:v>453</x:v>
+      </x:c>
+      <x:c r="C63" s="0" t="s">
+        <x:v>454</x:v>
+      </x:c>
+      <x:c r="D63" s="0" t="s">
+        <x:v>455</x:v>
+      </x:c>
+      <x:c r="E63" s="0" t="s">
+        <x:v>456</x:v>
+      </x:c>
+      <x:c r="F63" s="0" t="s">
+        <x:v>457</x:v>
+      </x:c>
+      <x:c r="G63" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H63" s="0" t="s">
+        <x:v>458</x:v>
+      </x:c>
+      <x:c r="I63" s="0" t="s">
+        <x:v>459</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="64" spans="1:9">
+      <x:c r="A64" s="0" t="s">
+        <x:v>460</x:v>
+      </x:c>
+      <x:c r="B64" s="0" t="s">
+        <x:v>461</x:v>
+      </x:c>
+      <x:c r="C64" s="0" t="s">
+        <x:v>462</x:v>
+      </x:c>
+      <x:c r="D64" s="0" t="s">
+        <x:v>463</x:v>
+      </x:c>
+      <x:c r="E64" s="0" t="s">
+        <x:v>464</x:v>
+      </x:c>
+      <x:c r="F64" s="0" t="s">
+        <x:v>465</x:v>
+      </x:c>
+      <x:c r="G64" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H64" s="0" t="s">
+        <x:v>466</x:v>
+      </x:c>
+      <x:c r="I64" s="0" t="s">
+        <x:v>467</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="65" spans="1:9">
+      <x:c r="A65" s="0" t="s">
+        <x:v>468</x:v>
+      </x:c>
+      <x:c r="B65" s="0" t="s">
+        <x:v>469</x:v>
+      </x:c>
+      <x:c r="C65" s="0" t="s">
+        <x:v>470</x:v>
+      </x:c>
+      <x:c r="D65" s="0" t="s">
+        <x:v>471</x:v>
+      </x:c>
+      <x:c r="E65" s="0" t="s">
+        <x:v>472</x:v>
+      </x:c>
+      <x:c r="F65" s="0" t="s">
+        <x:v>473</x:v>
+      </x:c>
+      <x:c r="G65" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H65" s="0" t="s">
+        <x:v>474</x:v>
+      </x:c>
+      <x:c r="I65" s="0" t="s">
+        <x:v>475</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="66" spans="1:9">
+      <x:c r="A66" s="0" t="s">
+        <x:v>476</x:v>
+      </x:c>
+      <x:c r="B66" s="0" t="s">
+        <x:v>477</x:v>
+      </x:c>
+      <x:c r="C66" s="0" t="s">
+        <x:v>478</x:v>
+      </x:c>
+      <x:c r="D66" s="0" t="s">
+        <x:v>479</x:v>
+      </x:c>
+      <x:c r="E66" s="0" t="s">
+        <x:v>480</x:v>
+      </x:c>
+      <x:c r="F66" s="0" t="s">
+        <x:v>481</x:v>
+      </x:c>
+      <x:c r="G66" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H66" s="0" t="s">
+        <x:v>482</x:v>
+      </x:c>
+      <x:c r="I66" s="0" t="s">
+        <x:v>483</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="67" spans="1:9">
+      <x:c r="A67" s="0" t="s">
+        <x:v>484</x:v>
+      </x:c>
+      <x:c r="B67" s="0" t="s">
+        <x:v>485</x:v>
+      </x:c>
+      <x:c r="C67" s="0" t="s">
+        <x:v>486</x:v>
+      </x:c>
+      <x:c r="D67" s="0" t="s">
+        <x:v>487</x:v>
+      </x:c>
+      <x:c r="E67" s="0" t="s">
+        <x:v>488</x:v>
+      </x:c>
+      <x:c r="F67" s="0" t="s">
+        <x:v>489</x:v>
+      </x:c>
+      <x:c r="G67" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H67" s="0" t="s">
+        <x:v>490</x:v>
+      </x:c>
+      <x:c r="I67" s="0" t="s">
+        <x:v>491</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="68" spans="1:9">
+      <x:c r="A68" s="0" t="s">
+        <x:v>492</x:v>
+      </x:c>
+      <x:c r="B68" s="0" t="s">
+        <x:v>493</x:v>
+      </x:c>
+      <x:c r="C68" s="0" t="s">
+        <x:v>494</x:v>
+      </x:c>
+      <x:c r="D68" s="0" t="s">
+        <x:v>495</x:v>
+      </x:c>
+      <x:c r="E68" s="0" t="s">
+        <x:v>496</x:v>
+      </x:c>
+      <x:c r="F68" s="0" t="s">
+        <x:v>497</x:v>
+      </x:c>
+      <x:c r="G68" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H68" s="0" t="s">
+        <x:v>498</x:v>
+      </x:c>
+      <x:c r="I68" s="0" t="s">
+        <x:v>499</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="69" spans="1:9">
+      <x:c r="A69" s="0" t="s">
+        <x:v>116</x:v>
+      </x:c>
+      <x:c r="B69" s="0" t="s">
+        <x:v>117</x:v>
+      </x:c>
+      <x:c r="C69" s="0" t="s">
+        <x:v>118</x:v>
+      </x:c>
+      <x:c r="D69" s="0" t="s">
+        <x:v>119</x:v>
+      </x:c>
+      <x:c r="E69" s="0" t="s">
+        <x:v>120</x:v>
+      </x:c>
+      <x:c r="F69" s="0" t="s">
+        <x:v>121</x:v>
+      </x:c>
+      <x:c r="G69" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H69" s="0" t="s">
+        <x:v>500</x:v>
+      </x:c>
+      <x:c r="I69" s="0" t="s">
+        <x:v>123</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="70" spans="1:9">
+      <x:c r="A70" s="0" t="s">
+        <x:v>501</x:v>
+      </x:c>
+      <x:c r="B70" s="0" t="s">
+        <x:v>502</x:v>
+      </x:c>
+      <x:c r="C70" s="0" t="s">
+        <x:v>503</x:v>
+      </x:c>
+      <x:c r="D70" s="0" t="s">
+        <x:v>504</x:v>
+      </x:c>
+      <x:c r="E70" s="0" t="s">
+        <x:v>505</x:v>
+      </x:c>
+      <x:c r="F70" s="0" t="s">
+        <x:v>506</x:v>
+      </x:c>
+      <x:c r="G70" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H70" s="0" t="s">
+        <x:v>507</x:v>
+      </x:c>
+      <x:c r="I70" s="0" t="s">
+        <x:v>508</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="71" spans="1:9">
+      <x:c r="A71" s="0" t="s">
+        <x:v>509</x:v>
+      </x:c>
+      <x:c r="B71" s="0" t="s">
+        <x:v>510</x:v>
+      </x:c>
+      <x:c r="C71" s="0" t="s">
+        <x:v>511</x:v>
+      </x:c>
+      <x:c r="D71" s="0" t="s">
+        <x:v>512</x:v>
+      </x:c>
+      <x:c r="E71" s="0" t="s">
+        <x:v>513</x:v>
+      </x:c>
+      <x:c r="F71" s="0" t="s">
+        <x:v>514</x:v>
+      </x:c>
+      <x:c r="G71" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H71" s="0" t="s">
+        <x:v>515</x:v>
+      </x:c>
+      <x:c r="I71" s="0" t="s">
+        <x:v>516</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="72" spans="1:9">
+      <x:c r="A72" s="0" t="s">
+        <x:v>189</x:v>
+      </x:c>
+      <x:c r="B72" s="0" t="s">
+        <x:v>190</x:v>
+      </x:c>
+      <x:c r="C72" s="0" t="s">
+        <x:v>191</x:v>
+      </x:c>
+      <x:c r="D72" s="0" t="s">
+        <x:v>192</x:v>
+      </x:c>
+      <x:c r="E72" s="0" t="s">
+        <x:v>193</x:v>
+      </x:c>
+      <x:c r="F72" s="0" t="s">
+        <x:v>194</x:v>
+      </x:c>
+      <x:c r="G72" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H72" s="0" t="s">
+        <x:v>517</x:v>
+      </x:c>
+      <x:c r="I72" s="0" t="s">
+        <x:v>196</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="73" spans="1:9">
+      <x:c r="A73" s="0" t="s">
+        <x:v>460</x:v>
+      </x:c>
+      <x:c r="B73" s="0" t="s">
+        <x:v>461</x:v>
+      </x:c>
+      <x:c r="C73" s="0" t="s">
+        <x:v>462</x:v>
+      </x:c>
+      <x:c r="D73" s="0" t="s">
+        <x:v>463</x:v>
+      </x:c>
+      <x:c r="E73" s="0" t="s">
+        <x:v>464</x:v>
+      </x:c>
+      <x:c r="F73" s="0" t="s">
+        <x:v>465</x:v>
+      </x:c>
+      <x:c r="G73" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H73" s="0" t="s">
+        <x:v>518</x:v>
+      </x:c>
+      <x:c r="I73" s="0" t="s">
+        <x:v>467</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="74" spans="1:9">
+      <x:c r="A74" s="0" t="s">
+        <x:v>519</x:v>
+      </x:c>
+      <x:c r="B74" s="0" t="s">
+        <x:v>520</x:v>
+      </x:c>
+      <x:c r="C74" s="0" t="s">
+        <x:v>521</x:v>
+      </x:c>
+      <x:c r="D74" s="0" t="s">
+        <x:v>522</x:v>
+      </x:c>
+      <x:c r="E74" s="0" t="s">
+        <x:v>523</x:v>
+      </x:c>
+      <x:c r="F74" s="0" t="s">
+        <x:v>524</x:v>
+      </x:c>
+      <x:c r="G74" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H74" s="0" t="s">
+        <x:v>525</x:v>
+      </x:c>
+      <x:c r="I74" s="0" t="s">
+        <x:v>526</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="75" spans="1:9">
+      <x:c r="A75" s="0" t="s">
+        <x:v>527</x:v>
+      </x:c>
+      <x:c r="B75" s="0" t="s">
+        <x:v>528</x:v>
+      </x:c>
+      <x:c r="C75" s="0" t="s">
+        <x:v>529</x:v>
+      </x:c>
+      <x:c r="D75" s="0" t="s">
+        <x:v>530</x:v>
+      </x:c>
+      <x:c r="E75" s="0" t="s">
+        <x:v>531</x:v>
+      </x:c>
+      <x:c r="F75" s="0" t="s">
+        <x:v>532</x:v>
+      </x:c>
+      <x:c r="G75" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H75" s="0" t="s">
+        <x:v>533</x:v>
+      </x:c>
+      <x:c r="I75" s="0" t="s">
+        <x:v>534</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="76" spans="1:9">
+      <x:c r="A76" s="0" t="s">
+        <x:v>51</x:v>
+      </x:c>
+      <x:c r="B76" s="0" t="s">
+        <x:v>52</x:v>
+      </x:c>
+      <x:c r="C76" s="0" t="s">
+        <x:v>53</x:v>
+      </x:c>
+      <x:c r="D76" s="0" t="s">
+        <x:v>54</x:v>
+      </x:c>
+      <x:c r="E76" s="0" t="s">
+        <x:v>55</x:v>
+      </x:c>
+      <x:c r="F76" s="0" t="s">
+        <x:v>56</x:v>
+      </x:c>
+      <x:c r="G76" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H76" s="0" t="s">
+        <x:v>535</x:v>
+      </x:c>
+      <x:c r="I76" s="0" t="s">
+        <x:v>59</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="77" spans="1:9">
+      <x:c r="A77" s="0" t="s">
+        <x:v>536</x:v>
+      </x:c>
+      <x:c r="B77" s="0" t="s">
+        <x:v>537</x:v>
+      </x:c>
+      <x:c r="C77" s="0" t="s">
+        <x:v>538</x:v>
+      </x:c>
+      <x:c r="D77" s="0" t="s">
+        <x:v>539</x:v>
+      </x:c>
+      <x:c r="E77" s="0" t="s">
+        <x:v>540</x:v>
+      </x:c>
+      <x:c r="F77" s="0" t="s">
+        <x:v>541</x:v>
+      </x:c>
+      <x:c r="G77" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H77" s="0" t="s">
+        <x:v>542</x:v>
+      </x:c>
+      <x:c r="I77" s="0" t="s">
+        <x:v>543</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="78" spans="1:9">
+      <x:c r="A78" s="0" t="s">
+        <x:v>544</x:v>
+      </x:c>
+      <x:c r="B78" s="0" t="s">
+        <x:v>545</x:v>
+      </x:c>
+      <x:c r="C78" s="0" t="s">
+        <x:v>546</x:v>
+      </x:c>
+      <x:c r="D78" s="0" t="s">
+        <x:v>547</x:v>
+      </x:c>
+      <x:c r="E78" s="0" t="s">
+        <x:v>548</x:v>
+      </x:c>
+      <x:c r="F78" s="0" t="s">
+        <x:v>549</x:v>
+      </x:c>
+      <x:c r="G78" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H78" s="0" t="s">
+        <x:v>550</x:v>
+      </x:c>
+      <x:c r="I78" s="0" t="s">
+        <x:v>551</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="79" spans="1:9">
+      <x:c r="A79" s="0" t="s">
+        <x:v>552</x:v>
+      </x:c>
+      <x:c r="B79" s="0" t="s">
+        <x:v>553</x:v>
+      </x:c>
+      <x:c r="C79" s="0" t="s">
+        <x:v>554</x:v>
+      </x:c>
+      <x:c r="D79" s="0" t="s">
+        <x:v>555</x:v>
+      </x:c>
+      <x:c r="E79" s="0" t="s">
+        <x:v>556</x:v>
+      </x:c>
+      <x:c r="F79" s="0" t="s">
+        <x:v>557</x:v>
+      </x:c>
+      <x:c r="G79" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H79" s="0" t="s">
+        <x:v>558</x:v>
+      </x:c>
+      <x:c r="I79" s="0" t="s">
+        <x:v>559</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="80" spans="1:9">
+      <x:c r="A80" s="0" t="s">
+        <x:v>560</x:v>
+      </x:c>
+      <x:c r="B80" s="0" t="s">
+        <x:v>561</x:v>
+      </x:c>
+      <x:c r="C80" s="0" t="s">
+        <x:v>562</x:v>
+      </x:c>
+      <x:c r="D80" s="0" t="s">
+        <x:v>563</x:v>
+      </x:c>
+      <x:c r="E80" s="0" t="s">
+        <x:v>564</x:v>
+      </x:c>
+      <x:c r="F80" s="0" t="s">
+        <x:v>565</x:v>
+      </x:c>
+      <x:c r="G80" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H80" s="0" t="s">
+        <x:v>566</x:v>
+      </x:c>
+      <x:c r="I80" s="0" t="s">
+        <x:v>567</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="81" spans="1:9">
+      <x:c r="A81" s="0" t="s">
+        <x:v>568</x:v>
+      </x:c>
+      <x:c r="B81" s="0" t="s">
+        <x:v>569</x:v>
+      </x:c>
+      <x:c r="C81" s="0" t="s">
+        <x:v>570</x:v>
+      </x:c>
+      <x:c r="D81" s="0" t="s">
+        <x:v>571</x:v>
+      </x:c>
+      <x:c r="E81" s="0" t="s">
+        <x:v>572</x:v>
+      </x:c>
+      <x:c r="F81" s="0" t="s">
+        <x:v>573</x:v>
+      </x:c>
+      <x:c r="G81" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H81" s="0" t="s">
+        <x:v>574</x:v>
+      </x:c>
+      <x:c r="I81" s="0" t="s">
+        <x:v>575</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="82" spans="1:9">
+      <x:c r="A82" s="0" t="s">
+        <x:v>576</x:v>
+      </x:c>
+      <x:c r="B82" s="0" t="s">
+        <x:v>577</x:v>
+      </x:c>
+      <x:c r="C82" s="0" t="s">
+        <x:v>578</x:v>
+      </x:c>
+      <x:c r="D82" s="0" t="s">
+        <x:v>579</x:v>
+      </x:c>
+      <x:c r="E82" s="0" t="s">
+        <x:v>580</x:v>
+      </x:c>
+      <x:c r="F82" s="0" t="s">
+        <x:v>581</x:v>
+      </x:c>
+      <x:c r="G82" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H82" s="0" t="s">
+        <x:v>582</x:v>
+      </x:c>
+      <x:c r="I82" s="0" t="s">
+        <x:v>583</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="83" spans="1:9">
+      <x:c r="A83" s="0" t="s">
+        <x:v>584</x:v>
+      </x:c>
+      <x:c r="B83" s="0" t="s">
+        <x:v>585</x:v>
+      </x:c>
+      <x:c r="C83" s="0" t="s">
+        <x:v>586</x:v>
+      </x:c>
+      <x:c r="D83" s="0" t="s">
+        <x:v>587</x:v>
+      </x:c>
+      <x:c r="E83" s="0" t="s">
+        <x:v>588</x:v>
+      </x:c>
+      <x:c r="F83" s="0" t="s">
+        <x:v>589</x:v>
+      </x:c>
+      <x:c r="G83" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H83" s="0" t="s">
+        <x:v>590</x:v>
+      </x:c>
+      <x:c r="I83" s="0" t="s">
+        <x:v>591</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="84" spans="1:9">
+      <x:c r="A84" s="0" t="s">
+        <x:v>592</x:v>
+      </x:c>
+      <x:c r="B84" s="0" t="s">
+        <x:v>593</x:v>
+      </x:c>
+      <x:c r="C84" s="0" t="s">
+        <x:v>594</x:v>
+      </x:c>
+      <x:c r="D84" s="0" t="s">
+        <x:v>595</x:v>
+      </x:c>
+      <x:c r="E84" s="0" t="s">
+        <x:v>596</x:v>
+      </x:c>
+      <x:c r="F84" s="0" t="s">
+        <x:v>597</x:v>
+      </x:c>
+      <x:c r="G84" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H84" s="0" t="s">
+        <x:v>598</x:v>
+      </x:c>
+      <x:c r="I84" s="0" t="s">
+        <x:v>599</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="85" spans="1:9">
+      <x:c r="A85" s="0" t="s">
+        <x:v>600</x:v>
+      </x:c>
+      <x:c r="B85" s="0" t="s">
+        <x:v>601</x:v>
+      </x:c>
+      <x:c r="C85" s="0" t="s">
+        <x:v>602</x:v>
+      </x:c>
+      <x:c r="D85" s="0" t="s">
+        <x:v>603</x:v>
+      </x:c>
+      <x:c r="E85" s="0" t="s">
+        <x:v>604</x:v>
+      </x:c>
+      <x:c r="F85" s="0" t="s">
+        <x:v>605</x:v>
+      </x:c>
+      <x:c r="G85" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H85" s="0" t="s">
+        <x:v>606</x:v>
+      </x:c>
+      <x:c r="I85" s="0" t="s">
+        <x:v>607</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="86" spans="1:9">
+      <x:c r="A86" s="0" t="s">
+        <x:v>608</x:v>
+      </x:c>
+      <x:c r="B86" s="0" t="s">
+        <x:v>609</x:v>
+      </x:c>
+      <x:c r="C86" s="0" t="s">
+        <x:v>610</x:v>
+      </x:c>
+      <x:c r="D86" s="0" t="s">
+        <x:v>611</x:v>
+      </x:c>
+      <x:c r="E86" s="0" t="s">
+        <x:v>612</x:v>
+      </x:c>
+      <x:c r="F86" s="0" t="s">
+        <x:v>613</x:v>
+      </x:c>
+      <x:c r="G86" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H86" s="0" t="s">
+        <x:v>614</x:v>
+      </x:c>
+      <x:c r="I86" s="0" t="s">
+        <x:v>615</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="87" spans="1:9">
+      <x:c r="A87" s="0" t="s">
+        <x:v>278</x:v>
+      </x:c>
+      <x:c r="B87" s="0" t="s">
+        <x:v>279</x:v>
+      </x:c>
+      <x:c r="C87" s="0" t="s">
+        <x:v>280</x:v>
+      </x:c>
+      <x:c r="D87" s="0" t="s">
+        <x:v>281</x:v>
+      </x:c>
+      <x:c r="E87" s="0" t="s">
+        <x:v>282</x:v>
+      </x:c>
+      <x:c r="F87" s="0" t="s">
+        <x:v>283</x:v>
+      </x:c>
+      <x:c r="G87" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H87" s="0" t="s">
+        <x:v>616</x:v>
+      </x:c>
+      <x:c r="I87" s="0" t="s">
+        <x:v>285</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="88" spans="1:9">
+      <x:c r="A88" s="0" t="s">
+        <x:v>108</x:v>
+      </x:c>
+      <x:c r="B88" s="0" t="s">
+        <x:v>109</x:v>
+      </x:c>
+      <x:c r="C88" s="0" t="s">
+        <x:v>110</x:v>
+      </x:c>
+      <x:c r="D88" s="0" t="s">
+        <x:v>111</x:v>
+      </x:c>
+      <x:c r="E88" s="0" t="s">
+        <x:v>112</x:v>
+      </x:c>
+      <x:c r="F88" s="0" t="s">
+        <x:v>113</x:v>
+      </x:c>
+      <x:c r="G88" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H88" s="0" t="s">
+        <x:v>617</x:v>
+      </x:c>
+      <x:c r="I88" s="0" t="s">
+        <x:v>115</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="89" spans="1:9">
+      <x:c r="A89" s="0" t="s">
+        <x:v>618</x:v>
+      </x:c>
+      <x:c r="B89" s="0" t="s">
+        <x:v>619</x:v>
+      </x:c>
+      <x:c r="C89" s="0" t="s">
+        <x:v>620</x:v>
+      </x:c>
+      <x:c r="D89" s="0" t="s">
+        <x:v>621</x:v>
+      </x:c>
+      <x:c r="E89" s="0" t="s">
+        <x:v>622</x:v>
+      </x:c>
+      <x:c r="F89" s="0" t="s">
+        <x:v>623</x:v>
+      </x:c>
+      <x:c r="G89" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H89" s="0" t="s">
+        <x:v>624</x:v>
+      </x:c>
+      <x:c r="I89" s="0" t="s">
+        <x:v>625</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="90" spans="1:9">
+      <x:c r="A90" s="0" t="s">
+        <x:v>436</x:v>
+      </x:c>
+      <x:c r="B90" s="0" t="s">
+        <x:v>437</x:v>
+      </x:c>
+      <x:c r="C90" s="0" t="s">
+        <x:v>438</x:v>
+      </x:c>
+      <x:c r="D90" s="0" t="s">
+        <x:v>439</x:v>
+      </x:c>
+      <x:c r="E90" s="0" t="s">
+        <x:v>440</x:v>
+      </x:c>
+      <x:c r="F90" s="0" t="s">
+        <x:v>441</x:v>
+      </x:c>
+      <x:c r="G90" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H90" s="0" t="s">
+        <x:v>626</x:v>
+      </x:c>
+      <x:c r="I90" s="0" t="s">
+        <x:v>443</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="91" spans="1:9">
+      <x:c r="A91" s="0" t="s">
+        <x:v>627</x:v>
+      </x:c>
+      <x:c r="B91" s="0" t="s">
+        <x:v>628</x:v>
+      </x:c>
+      <x:c r="C91" s="0" t="s">
+        <x:v>629</x:v>
+      </x:c>
+      <x:c r="D91" s="0" t="s">
+        <x:v>630</x:v>
+      </x:c>
+      <x:c r="E91" s="0" t="s">
+        <x:v>631</x:v>
+      </x:c>
+      <x:c r="F91" s="0" t="s">
+        <x:v>632</x:v>
+      </x:c>
+      <x:c r="G91" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H91" s="0" t="s">
+        <x:v>633</x:v>
+      </x:c>
+      <x:c r="I91" s="0" t="s">
+        <x:v>634</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="92" spans="1:9">
+      <x:c r="A92" s="0" t="s">
+        <x:v>635</x:v>
+      </x:c>
+      <x:c r="B92" s="0" t="s">
+        <x:v>636</x:v>
+      </x:c>
+      <x:c r="C92" s="0" t="s">
+        <x:v>637</x:v>
+      </x:c>
+      <x:c r="D92" s="0" t="s">
+        <x:v>638</x:v>
+      </x:c>
+      <x:c r="E92" s="0" t="s">
+        <x:v>639</x:v>
+      </x:c>
+      <x:c r="F92" s="0" t="s">
+        <x:v>640</x:v>
+      </x:c>
+      <x:c r="G92" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H92" s="0" t="s">
+        <x:v>641</x:v>
+      </x:c>
+      <x:c r="I92" s="0" t="s">
+        <x:v>642</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="93" spans="1:9">
+      <x:c r="A93" s="0" t="s">
+        <x:v>643</x:v>
+      </x:c>
+      <x:c r="B93" s="0" t="s">
+        <x:v>644</x:v>
+      </x:c>
+      <x:c r="C93" s="0" t="s">
+        <x:v>645</x:v>
+      </x:c>
+      <x:c r="D93" s="0" t="s">
+        <x:v>646</x:v>
+      </x:c>
+      <x:c r="E93" s="0" t="s">
+        <x:v>647</x:v>
+      </x:c>
+      <x:c r="F93" s="0" t="s">
+        <x:v>648</x:v>
+      </x:c>
+      <x:c r="G93" s="0" t="s">
+        <x:v>57</x:v>
+      </x:c>
+      <x:c r="H93" s="0" t="s">
+        <x:v>649</x:v>
+      </x:c>
+      <x:c r="I93" s="0" t="s">
+        <x:v>650</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="94" spans="1:9">
+      <x:c r="A94" s="0" t="s">
+        <x:v>651</x:v>
+      </x:c>
+      <x:c r="B94" s="0" t="s">
+        <x:v>652</x:v>
+      </x:c>
+      <x:c r="C94" s="0" t="s">
+        <x:v>653</x:v>
+      </x:c>
+      <x:c r="D94" s="0" t="s">
+        <x:v>654</x:v>
+      </x:c>
+      <x:c r="E94" s="0" t="s">
+        <x:v>655</x:v>
+      </x:c>
+      <x:c r="F94" s="0" t="s">
+        <x:v>656</x:v>
+      </x:c>
+      <x:c r="G94" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H94" s="0" t="s">
+        <x:v>657</x:v>
+      </x:c>
+      <x:c r="I94" s="0" t="s">
+        <x:v>658</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="95" spans="1:9">
+      <x:c r="A95" s="0" t="s">
+        <x:v>659</x:v>
+      </x:c>
+      <x:c r="B95" s="0" t="s">
+        <x:v>660</x:v>
+      </x:c>
+      <x:c r="C95" s="0" t="s">
+        <x:v>661</x:v>
+      </x:c>
+      <x:c r="D95" s="0" t="s">
+        <x:v>662</x:v>
+      </x:c>
+      <x:c r="E95" s="0" t="s">
+        <x:v>663</x:v>
+      </x:c>
+      <x:c r="F95" s="0" t="s">
+        <x:v>664</x:v>
+      </x:c>
+      <x:c r="G95" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H95" s="0" t="s">
+        <x:v>665</x:v>
+      </x:c>
+      <x:c r="I95" s="0" t="s">
+        <x:v>666</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="96" spans="1:9">
+      <x:c r="A96" s="0" t="s">
+        <x:v>667</x:v>
+      </x:c>
+      <x:c r="B96" s="0" t="s">
+        <x:v>668</x:v>
+      </x:c>
+      <x:c r="C96" s="0" t="s">
+        <x:v>669</x:v>
+      </x:c>
+      <x:c r="D96" s="0" t="s">
+        <x:v>670</x:v>
+      </x:c>
+      <x:c r="E96" s="0" t="s">
+        <x:v>671</x:v>
+      </x:c>
+      <x:c r="F96" s="0" t="s">
+        <x:v>672</x:v>
+      </x:c>
+      <x:c r="G96" s="0" t="s">
+        <x:v>24</x:v>
+      </x:c>
+      <x:c r="H96" s="0" t="s">
+        <x:v>673</x:v>
+      </x:c>
+      <x:c r="I96" s="0" t="s">
+        <x:v>674</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="97" spans="1:9">
+      <x:c r="A97" s="0" t="s">
+        <x:v>675</x:v>
+      </x:c>
+      <x:c r="B97" s="0" t="s">
+        <x:v>676</x:v>
+      </x:c>
+      <x:c r="C97" s="0" t="s">
+        <x:v>677</x:v>
+      </x:c>
+      <x:c r="D97" s="0" t="s">
+        <x:v>678</x:v>
+      </x:c>
+      <x:c r="E97" s="0" t="s">
+        <x:v>679</x:v>
+      </x:c>
+      <x:c r="F97" s="0" t="s">
+        <x:v>680</x:v>
+      </x:c>
+      <x:c r="G97" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H97" s="0" t="s">
+        <x:v>681</x:v>
+      </x:c>
+      <x:c r="I97" s="0" t="s">
+        <x:v>682</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="98" spans="1:9">
+      <x:c r="A98" s="0" t="s">
+        <x:v>683</x:v>
+      </x:c>
+      <x:c r="B98" s="0" t="s">
+        <x:v>684</x:v>
+      </x:c>
+      <x:c r="C98" s="0" t="s">
+        <x:v>685</x:v>
+      </x:c>
+      <x:c r="D98" s="0" t="s">
+        <x:v>686</x:v>
+      </x:c>
+      <x:c r="E98" s="0" t="s">
+        <x:v>663</x:v>
+      </x:c>
+      <x:c r="F98" s="0" t="s">
+        <x:v>687</x:v>
+      </x:c>
+      <x:c r="G98" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H98" s="0" t="s">
+        <x:v>688</x:v>
+      </x:c>
+      <x:c r="I98" s="0" t="s">
+        <x:v>689</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="99" spans="1:9">
+      <x:c r="A99" s="0" t="s">
+        <x:v>690</x:v>
+      </x:c>
+      <x:c r="B99" s="0" t="s">
+        <x:v>691</x:v>
+      </x:c>
+      <x:c r="C99" s="0" t="s">
+        <x:v>692</x:v>
+      </x:c>
+      <x:c r="D99" s="0" t="s">
+        <x:v>693</x:v>
+      </x:c>
+      <x:c r="E99" s="0" t="s">
+        <x:v>663</x:v>
+      </x:c>
+      <x:c r="F99" s="0" t="s">
+        <x:v>694</x:v>
+      </x:c>
+      <x:c r="G99" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H99" s="0" t="s">
+        <x:v>695</x:v>
+      </x:c>
+      <x:c r="I99" s="0" t="s">
+        <x:v>696</x:v>
+      </x:c>
+    </x:row>
+    <x:row r="100" spans="1:9">
+      <x:c r="A100" s="0" t="s">
+        <x:v>697</x:v>
+      </x:c>
+      <x:c r="B100" s="0" t="s">
+        <x:v>698</x:v>
+      </x:c>
+      <x:c r="C100" s="0" t="s">
+        <x:v>699</x:v>
+      </x:c>
+      <x:c r="D100" s="0" t="s">
+        <x:v>700</x:v>
+      </x:c>
+      <x:c r="E100" s="0" t="s">
+        <x:v>701</x:v>
+      </x:c>
+      <x:c r="F100" s="0" t="s">
+        <x:v>702</x:v>
+      </x:c>
+      <x:c r="G100" s="0" t="s">
+        <x:v>15</x:v>
+      </x:c>
+      <x:c r="H100" s="0" t="s">
+        <x:v>703</x:v>
+      </x:c>
+      <x:c r="I100" s="0" t="s">
+        <x:v>704</x:v>
       </x:c>
     </x:row>
   </x:sheetData>

--- a/cidadesss.xlsx
+++ b/cidadesss.xlsx
@@ -14,7 +14,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="705" uniqueCount="705">
+<x:sst xmlns:x="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="711" uniqueCount="711">
   <x:si>
     <x:t>Populaçao estimada</x:t>
   </x:si>
@@ -46,12 +46,10 @@
     <x:t>7006</x:t>
   </x:si>
   <x:si>
-    <x:t>6.704
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>7,61
-    hab/km²</x:t>
+    <x:t>6.704</x:t>
+  </x:si>
+  <x:si>
+    <x:t>7,61</x:t>
   </x:si>
   <x:si>
     <x:t>3100104</x:t>
@@ -60,7 +58,9 @@
     <x:t>abadiense</x:t>
   </x:si>
   <x:si>
-    <x:t>WANDERLEI LEMES SANTOS</x:t>
+    <x:t xml:space="preserve">
+                WANDERLEI LEMES SANTOS 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>1</x:t>
@@ -75,12 +75,10 @@
     <x:t>23250</x:t>
   </x:si>
   <x:si>
-    <x:t>22.690
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12,49
-    hab/km²</x:t>
+    <x:t>22.690</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12,49</x:t>
   </x:si>
   <x:si>
     <x:t>3100203</x:t>
@@ -89,7 +87,9 @@
     <x:t>abaetense</x:t>
   </x:si>
   <x:si>
-    <x:t>IVANIR DELADIER DA COSTA</x:t>
+    <x:t xml:space="preserve">
+                IVANIR DELADIER DA COSTA 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>2</x:t>
@@ -104,21 +104,21 @@
     <x:t>12335</x:t>
   </x:si>
   <x:si>
-    <x:t>11.885
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8,79
-    hab/km²</x:t>
+    <x:t>11.885</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8,79</x:t>
   </x:si>
   <x:si>
     <x:t>3155504</x:t>
   </x:si>
   <x:si>
-    <x:t>rio-paraibano</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VALDEMIR DIOGENES DA SILVA</x:t>
+    <x:t>rioparaibano</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">
+                VALDEMIR DIOGENES DA SILVA 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>38812-000</x:t>
@@ -130,21 +130,21 @@
     <x:t>13444</x:t>
   </x:si>
   <x:si>
-    <x:t>13.311
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28,29
-    hab/km²</x:t>
+    <x:t>13.311</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28,29</x:t>
   </x:si>
   <x:si>
     <x:t>3100302</x:t>
   </x:si>
   <x:si>
-    <x:t>abre-campense</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VITOR HENRIQUE MOREIRA FERREIRA DE OLIVEIRA</x:t>
+    <x:t>abrecampense</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">
+                VITOR HENRIQUE MOREIRA FERREIRA DE OLIVEIRA 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>35365-000</x:t>
@@ -156,12 +156,10 @@
     <x:t>3994</x:t>
   </x:si>
   <x:si>
-    <x:t>3.920
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>38,47
-    hab/km²</x:t>
+    <x:t>3.920</x:t>
+  </x:si>
+  <x:si>
+    <x:t>38,47</x:t>
   </x:si>
   <x:si>
     <x:t>3100401</x:t>
@@ -170,7 +168,9 @@
     <x:t>acaiaquense</x:t>
   </x:si>
   <x:si>
-    <x:t>LUIZ CARLOS FAUSTINO</x:t>
+    <x:t xml:space="preserve">
+                LUIZ CARLOS FAUSTINO 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>35438-000</x:t>
@@ -182,12 +182,10 @@
     <x:t>52446</x:t>
   </x:si>
   <x:si>
-    <x:t>45.449
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>83,76
-    hab/km²</x:t>
+    <x:t>45.449</x:t>
+  </x:si>
+  <x:si>
+    <x:t>83,76</x:t>
   </x:si>
   <x:si>
     <x:t>3131901</x:t>
@@ -196,7 +194,9 @@
     <x:t>itabiritense</x:t>
   </x:si>
   <x:si>
-    <x:t>ORLANDO AMORIM CALDEIRA</x:t>
+    <x:t xml:space="preserve">
+                ORLANDO AMORIM CALDEIRA 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>3</x:t>
@@ -211,12 +211,10 @@
     <x:t>6288</x:t>
   </x:si>
   <x:si>
-    <x:t>6.497
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4,14
-    hab/km²</x:t>
+    <x:t>6.497</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4,14</x:t>
   </x:si>
   <x:si>
     <x:t>3108503</x:t>
@@ -225,7 +223,9 @@
     <x:t>botumiriense</x:t>
   </x:si>
   <x:si>
-    <x:t>ANA PEREIRA NETA</x:t>
+    <x:t xml:space="preserve">
+                ANA PEREIRA NETA 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>39597-000</x:t>
@@ -237,12 +237,10 @@
     <x:t>25141</x:t>
   </x:si>
   <x:si>
-    <x:t>24.959
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18,50
-    hab/km²</x:t>
+    <x:t>24.959</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18,50</x:t>
   </x:si>
   <x:si>
     <x:t>3101102</x:t>
@@ -251,7 +249,9 @@
     <x:t>aimorense</x:t>
   </x:si>
   <x:si>
-    <x:t>MARCELO MARQUES</x:t>
+    <x:t xml:space="preserve">
+                MARCELO MARQUES 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>35200-000</x:t>
@@ -263,12 +263,10 @@
     <x:t>5976</x:t>
   </x:si>
   <x:si>
-    <x:t>6.162
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9,48
-    hab/km²</x:t>
+    <x:t>6.162</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9,48</x:t>
   </x:si>
   <x:si>
     <x:t>3101201</x:t>
@@ -277,7 +275,9 @@
     <x:t>aiuruocano</x:t>
   </x:si>
   <x:si>
-    <x:t>ERLISSON VITOR LOPES</x:t>
+    <x:t xml:space="preserve">
+                ERLISSON VITOR LOPES 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>37450-000</x:t>
@@ -289,12 +289,10 @@
     <x:t>2665</x:t>
   </x:si>
   <x:si>
-    <x:t>2.709
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16,79
-    hab/km²</x:t>
+    <x:t>2.709</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16,79</x:t>
   </x:si>
   <x:si>
     <x:t>3101300</x:t>
@@ -303,7 +301,9 @@
     <x:t>alagoense</x:t>
   </x:si>
   <x:si>
-    <x:t>JULIANO DINIZ DE OLIVEIRA</x:t>
+    <x:t xml:space="preserve">
+                JULIANO DINIZ DE OLIVEIRA 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>37458-000</x:t>
@@ -315,12 +315,10 @@
     <x:t>3011</x:t>
   </x:si>
   <x:si>
-    <x:t>2.913
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>50,22
-    hab/km²</x:t>
+    <x:t>2.913</x:t>
+  </x:si>
+  <x:si>
+    <x:t>50,22</x:t>
   </x:si>
   <x:si>
     <x:t>3101409</x:t>
@@ -329,7 +327,9 @@
     <x:t>albertinense</x:t>
   </x:si>
   <x:si>
-    <x:t>JOÃO PAULO FACANALI DE OLIVEIRA</x:t>
+    <x:t xml:space="preserve">
+                JOÃO PAULO FACANALI DE OLIVEIRA 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>37596-000</x:t>
@@ -341,21 +341,21 @@
     <x:t>13443</x:t>
   </x:si>
   <x:si>
-    <x:t>12.611
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12,03
-    hab/km²</x:t>
+    <x:t>12.611</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12,03</x:t>
   </x:si>
   <x:si>
     <x:t>3140506</x:t>
   </x:si>
   <x:si>
-    <x:t>martinho-campense</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WILSON CORREA ALVES AFONSO DE CARVALHO</x:t>
+    <x:t>martinhocampense</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">
+                WILSON CORREA ALVES AFONSO DE CARVALHO 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>35608-000</x:t>
@@ -367,12 +367,10 @@
     <x:t>67822</x:t>
   </x:si>
   <x:si>
-    <x:t>65.128
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43,36
-    hab/km²</x:t>
+    <x:t>65.128</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43,36</x:t>
   </x:si>
   <x:si>
     <x:t>3126109</x:t>
@@ -381,7 +379,9 @@
     <x:t>formiguense</x:t>
   </x:si>
   <x:si>
-    <x:t>EUGÊNIO VILELA JÚNIOR</x:t>
+    <x:t xml:space="preserve">
+                EUGÊNIO VILELA JÚNIOR 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>35579-400</x:t>
@@ -393,21 +393,21 @@
     <x:t>22949</x:t>
   </x:si>
   <x:si>
-    <x:t>22.242
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14,99
-    hab/km²</x:t>
+    <x:t>22.242</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14,99</x:t>
   </x:si>
   <x:si>
     <x:t>3118403</x:t>
   </x:si>
   <x:si>
-    <x:t>conselheiro-penense</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NADIA FILOMENA DUTRA FRANCA</x:t>
+    <x:t>conselheiropenense</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">
+                NADIA FILOMENA DUTRA FRANCA 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>35245-000</x:t>
@@ -419,12 +419,10 @@
     <x:t>27966</x:t>
   </x:si>
   <x:si>
-    <x:t>27.547
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8,31
-    hab/km²</x:t>
+    <x:t>27.547</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8,31</x:t>
   </x:si>
   <x:si>
     <x:t>3119302</x:t>
@@ -433,7 +431,9 @@
     <x:t>coromandelense</x:t>
   </x:si>
   <x:si>
-    <x:t>FERNANDO BRENO VALADARES VIEIRA</x:t>
+    <x:t xml:space="preserve">
+                FERNANDO BRENO VALADARES VIEIRA 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>38560-000</x:t>
@@ -445,12 +445,10 @@
     <x:t>39690</x:t>
   </x:si>
   <x:si>
-    <x:t>34.456
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24,53
-    hab/km²</x:t>
+    <x:t>34.456</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24,53</x:t>
   </x:si>
   <x:si>
     <x:t>3134400</x:t>
@@ -459,7 +457,9 @@
     <x:t>ituramense</x:t>
   </x:si>
   <x:si>
-    <x:t>CLAUDIO TOMAZ DE FREITAS</x:t>
+    <x:t xml:space="preserve">
+                CLAUDIO TOMAZ DE FREITAS 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>38282-000</x:t>
@@ -471,12 +471,10 @@
     <x:t>20418</x:t>
   </x:si>
   <x:si>
-    <x:t>17.134
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15,37
-    hab/km²</x:t>
+    <x:t>17.134</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15,37</x:t>
   </x:si>
   <x:si>
     <x:t>3134608</x:t>
@@ -485,7 +483,9 @@
     <x:t>jaboticatubense</x:t>
   </x:si>
   <x:si>
-    <x:t>ENEIMAR ADRIANO MARQUES</x:t>
+    <x:t xml:space="preserve">
+                ENEIMAR ADRIANO MARQUES 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>35835-000</x:t>
@@ -497,12 +497,10 @@
     <x:t>7436</x:t>
   </x:si>
   <x:si>
-    <x:t>7.172
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>42,95
-    hab/km²</x:t>
+    <x:t>7.172</x:t>
+  </x:si>
+  <x:si>
+    <x:t>42,95</x:t>
   </x:si>
   <x:si>
     <x:t>3101805</x:t>
@@ -511,7 +509,9 @@
     <x:t>alpercatense</x:t>
   </x:si>
   <x:si>
-    <x:t>RAFAEL AUGUSTO FRANCA OLIVEIRA MACHADO</x:t>
+    <x:t xml:space="preserve">
+                RAFAEL AUGUSTO FRANCA OLIVEIRA MACHADO 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>35138-000</x:t>
@@ -523,12 +523,10 @@
     <x:t>19958</x:t>
   </x:si>
   <x:si>
-    <x:t>18.488
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>40,66
-    hab/km²</x:t>
+    <x:t>18.488</x:t>
+  </x:si>
+  <x:si>
+    <x:t>40,66</x:t>
   </x:si>
   <x:si>
     <x:t>3101904</x:t>
@@ -537,7 +535,9 @@
     <x:t>alpinopolense</x:t>
   </x:si>
   <x:si>
-    <x:t>RAFAEL HENRIQUE DA SILVA FREIRE</x:t>
+    <x:t xml:space="preserve">
+                RAFAEL HENRIQUE DA SILVA FREIRE 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>37940-000</x:t>
@@ -552,12 +552,10 @@
     <x:t>281046</x:t>
   </x:si>
   <x:si>
-    <x:t>263.689
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>112,58
-    hab/km²</x:t>
+    <x:t>263.689</x:t>
+  </x:si>
+  <x:si>
+    <x:t>112,58</x:t>
   </x:si>
   <x:si>
     <x:t>3127701</x:t>
@@ -566,7 +564,9 @@
     <x:t>valadarense</x:t>
   </x:si>
   <x:si>
-    <x:t>ANDRÉ LUIZ COELHO MERLO</x:t>
+    <x:t xml:space="preserve">
+                ANDRÉ LUIZ COELHO MERLO 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>35102-000</x:t>
@@ -578,12 +578,10 @@
     <x:t>7766</x:t>
   </x:si>
   <x:si>
-    <x:t>8.012
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>10,61
-    hab/km²</x:t>
+    <x:t>8.012</x:t>
+  </x:si>
+  <x:si>
+    <x:t>10,61</x:t>
   </x:si>
   <x:si>
     <x:t>3553500</x:t>
@@ -592,7 +590,9 @@
     <x:t>tapiraiense</x:t>
   </x:si>
   <x:si>
-    <x:t>ARALDO TODESCO</x:t>
+    <x:t xml:space="preserve">
+                ARALDO TODESCO 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>38985-000</x:t>
@@ -604,12 +604,10 @@
     <x:t>3844</x:t>
   </x:si>
   <x:si>
-    <x:t>4.444
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15,98
-    hab/km²</x:t>
+    <x:t>4.444</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15,98</x:t>
   </x:si>
   <x:si>
     <x:t>3102209</x:t>
@@ -618,7 +616,9 @@
     <x:t>alvarenguense</x:t>
   </x:si>
   <x:si>
-    <x:t>DIOCÉLIO FERNANDO RIBEIRO</x:t>
+    <x:t xml:space="preserve">
+                DIOCÉLIO FERNANDO RIBEIRO 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>35249-000</x:t>
@@ -630,12 +630,10 @@
     <x:t>15169</x:t>
   </x:si>
   <x:si>
-    <x:t>15.261
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25,46
-    hab/km²</x:t>
+    <x:t>15.261</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25,46</x:t>
   </x:si>
   <x:si>
     <x:t>3102308</x:t>
@@ -644,7 +642,9 @@
     <x:t>alvinopolense</x:t>
   </x:si>
   <x:si>
-    <x:t>MAUROSAN GONÇALVES MACHADO</x:t>
+    <x:t xml:space="preserve">
+                MAUROSAN GONÇALVES MACHADO 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>35950-000</x:t>
@@ -656,12 +656,10 @@
     <x:t>7803</x:t>
   </x:si>
   <x:si>
-    <x:t>7.913
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>14,23
-    hab/km²</x:t>
+    <x:t>7.913</x:t>
+  </x:si>
+  <x:si>
+    <x:t>14,23</x:t>
   </x:si>
   <x:si>
     <x:t>3105004</x:t>
@@ -670,7 +668,9 @@
     <x:t>baldinense</x:t>
   </x:si>
   <x:si>
-    <x:t>FABRICIO ANDRADE MAGALHÃES</x:t>
+    <x:t xml:space="preserve">
+                FABRICIO ANDRADE MAGALHÃES 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>35734-000</x:t>
@@ -682,12 +682,10 @@
     <x:t>117825</x:t>
   </x:si>
   <x:si>
-    <x:t>109.801
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>40,23
-    hab/km²</x:t>
+    <x:t>109.801</x:t>
+  </x:si>
+  <x:si>
+    <x:t>40,23</x:t>
   </x:si>
   <x:si>
     <x:t>3103504</x:t>
@@ -696,7 +694,9 @@
     <x:t>araguarino</x:t>
   </x:si>
   <x:si>
-    <x:t>RENATO CARVALHO FERNANDES</x:t>
+    <x:t xml:space="preserve">
+                RENATO CARVALHO FERNANDES 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>38455-000</x:t>
@@ -708,21 +708,21 @@
     <x:t>74558</x:t>
   </x:si>
   <x:si>
-    <x:t>70.281
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>56,41
-    hab/km²</x:t>
+    <x:t>70.281</x:t>
+  </x:si>
+  <x:si>
+    <x:t>56,41</x:t>
   </x:si>
   <x:si>
     <x:t>3146107</x:t>
   </x:si>
   <x:si>
-    <x:t>ouro-pretano</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ANGELO OSWALDO DE ARAUJO SANTOS</x:t>
+    <x:t>ouropretano</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">
+                ANGELO OSWALDO DE ARAUJO SANTOS 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>35412-000</x:t>
@@ -734,12 +734,10 @@
     <x:t>41396</x:t>
   </x:si>
   <x:si>
-    <x:t>37.270
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>79,40
-    hab/km²</x:t>
+    <x:t>37.270</x:t>
+  </x:si>
+  <x:si>
+    <x:t>79,40</x:t>
   </x:si>
   <x:si>
     <x:t>3102605</x:t>
@@ -748,7 +746,9 @@
     <x:t>andradense</x:t>
   </x:si>
   <x:si>
-    <x:t>MARGOT NAVARRO GRAZIANI PIOLI</x:t>
+    <x:t xml:space="preserve">
+                MARGOT NAVARRO GRAZIANI PIOLI 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>37795-000</x:t>
@@ -760,12 +760,10 @@
     <x:t>8557</x:t>
   </x:si>
   <x:si>
-    <x:t>8.003
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43,21
-    hab/km²</x:t>
+    <x:t>8.003</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43,21</x:t>
   </x:si>
   <x:si>
     <x:t>3102852</x:t>
@@ -774,7 +772,9 @@
     <x:t>angelandense</x:t>
   </x:si>
   <x:si>
-    <x:t>JOÃO PAULO BATISTA DE SOUZA</x:t>
+    <x:t xml:space="preserve">
+                JOÃO PAULO BATISTA DE SOUZA 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>39685-000</x:t>
@@ -786,12 +786,10 @@
     <x:t>80616</x:t>
   </x:si>
   <x:si>
-    <x:t>74.219
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22,50
-    hab/km²</x:t>
+    <x:t>74.219</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22,50</x:t>
   </x:si>
   <x:si>
     <x:t>3120904</x:t>
@@ -800,7 +798,9 @@
     <x:t>curvelano</x:t>
   </x:si>
   <x:si>
-    <x:t>LUIZ PAULO GLORIA GUIMARAES</x:t>
+    <x:t xml:space="preserve">
+                LUIZ PAULO GLORIA GUIMARAES 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>35798-400</x:t>
@@ -812,12 +812,10 @@
     <x:t>11005</x:t>
   </x:si>
   <x:si>
-    <x:t>9.264
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>42,43
-    hab/km²</x:t>
+    <x:t>9.264</x:t>
+  </x:si>
+  <x:si>
+    <x:t>42,43</x:t>
   </x:si>
   <x:si>
     <x:t>3130200</x:t>
@@ -826,7 +824,9 @@
     <x:t>igaratinguense</x:t>
   </x:si>
   <x:si>
-    <x:t>FABIO ALVES COSTA FONSECA</x:t>
+    <x:t xml:space="preserve">
+                FABIO ALVES COSTA FONSECA 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>35698-000</x:t>
@@ -838,21 +838,21 @@
     <x:t>9275</x:t>
   </x:si>
   <x:si>
-    <x:t>9.565
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12,15
-    hab/km²</x:t>
+    <x:t>9.565</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12,15</x:t>
   </x:si>
   <x:si>
     <x:t>3103009</x:t>
   </x:si>
   <x:si>
-    <x:t>antônio-diense</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BENEDITO DE ASSIS LIMA</x:t>
+    <x:t>antniodiense</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">
+                BENEDITO DE ASSIS LIMA 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>35177-000</x:t>
@@ -864,12 +864,10 @@
     <x:t>5338</x:t>
   </x:si>
   <x:si>
-    <x:t>5.800
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8,09
-    hab/km²</x:t>
+    <x:t>5.800</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8,09</x:t>
   </x:si>
   <x:si>
     <x:t>3126752</x:t>
@@ -878,7 +876,9 @@
     <x:t>franciscopolitano</x:t>
   </x:si>
   <x:si>
-    <x:t>NILTON DOS SANTOS COIMBRA</x:t>
+    <x:t xml:space="preserve">
+                NILTON DOS SANTOS COIMBRA 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>39697-000</x:t>
@@ -893,12 +893,10 @@
     <x:t>45047</x:t>
   </x:si>
   <x:si>
-    <x:t>40.750
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>75,11
-    hab/km²</x:t>
+    <x:t>40.750</x:t>
+  </x:si>
+  <x:si>
+    <x:t>75,11</x:t>
   </x:si>
   <x:si>
     <x:t>3110004</x:t>
@@ -907,7 +905,9 @@
     <x:t>caeteense</x:t>
   </x:si>
   <x:si>
-    <x:t>LUCAS COELHO FERREIRA</x:t>
+    <x:t xml:space="preserve">
+                LUCAS COELHO FERREIRA 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>34960-000</x:t>
@@ -919,12 +919,10 @@
     <x:t>60012</x:t>
   </x:si>
   <x:si>
-    <x:t>53.468
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22,03
-    hab/km²</x:t>
+    <x:t>53.468</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22,03</x:t>
   </x:si>
   <x:si>
     <x:t>3127107</x:t>
@@ -933,7 +931,9 @@
     <x:t>frutalense</x:t>
   </x:si>
   <x:si>
-    <x:t>BRUNO AUGUSTO DE JESUS FERREIRA</x:t>
+    <x:t xml:space="preserve">
+                BRUNO AUGUSTO DE JESUS FERREIRA 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>38208-300</x:t>
@@ -945,12 +945,10 @@
     <x:t>9368</x:t>
   </x:si>
   <x:si>
-    <x:t>10.276
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12,60
-    hab/km²</x:t>
+    <x:t>10.276</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12,60</x:t>
   </x:si>
   <x:si>
     <x:t>3100500</x:t>
@@ -959,7 +957,9 @@
     <x:t>açucenense</x:t>
   </x:si>
   <x:si>
-    <x:t>RAULISSON MORAIS</x:t>
+    <x:t xml:space="preserve">
+                RAULISSON MORAIS 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>35147-100</x:t>
@@ -971,12 +971,10 @@
     <x:t>40666</x:t>
   </x:si>
   <x:si>
-    <x:t>33.973
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>53,13
-    hab/km²</x:t>
+    <x:t>33.973</x:t>
+  </x:si>
+  <x:si>
+    <x:t>53,13</x:t>
   </x:si>
   <x:si>
     <x:t>3109006</x:t>
@@ -985,7 +983,9 @@
     <x:t>brumadinhense</x:t>
   </x:si>
   <x:si>
-    <x:t>AVIMAR DE MELO BARCELOS</x:t>
+    <x:t xml:space="preserve">
+                AVIMAR DE MELO BARCELOS 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>35462-000</x:t>
@@ -997,12 +997,10 @@
     <x:t>2787</x:t>
   </x:si>
   <x:si>
-    <x:t>2.823
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>31,57
-    hab/km²</x:t>
+    <x:t>2.823</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31,57</x:t>
   </x:si>
   <x:si>
     <x:t>3103603</x:t>
@@ -1011,7 +1009,9 @@
     <x:t>arantinense</x:t>
   </x:si>
   <x:si>
-    <x:t>EDIMAR LUIS DE OLIVEIRA</x:t>
+    <x:t xml:space="preserve">
+                EDIMAR LUIS DE OLIVEIRA 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>37360-000</x:t>
@@ -1023,12 +1023,10 @@
     <x:t>6931</x:t>
   </x:si>
   <x:si>
-    <x:t>6.144
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20,77
-    hab/km²</x:t>
+    <x:t>6.144</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20,77</x:t>
   </x:si>
   <x:si>
     <x:t>3103751</x:t>
@@ -1037,7 +1035,9 @@
     <x:t>araporense</x:t>
   </x:si>
   <x:si>
-    <x:t>RENATA CRISTINA SILVA BORGES</x:t>
+    <x:t xml:space="preserve">
+                RENATA CRISTINA SILVA BORGES 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>38465-000</x:t>
@@ -1049,12 +1049,10 @@
     <x:t>2835</x:t>
   </x:si>
   <x:si>
-    <x:t>2.775
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15,96
-    hab/km²</x:t>
+    <x:t>2.775</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15,96</x:t>
   </x:si>
   <x:si>
     <x:t>3103801</x:t>
@@ -1063,7 +1061,9 @@
     <x:t>arapuaense</x:t>
   </x:si>
   <x:si>
-    <x:t>JOAO BATISTA TERTO DA CUNHA</x:t>
+    <x:t xml:space="preserve">
+                JOAO BATISTA TERTO DA CUNHA 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>38860-000</x:t>
@@ -1075,12 +1075,10 @@
     <x:t>2354</x:t>
   </x:si>
   <x:si>
-    <x:t>2.243
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>12,02
-    hab/km²</x:t>
+    <x:t>2.243</x:t>
+  </x:si>
+  <x:si>
+    <x:t>12,02</x:t>
   </x:si>
   <x:si>
     <x:t>3103207</x:t>
@@ -1089,7 +1087,9 @@
     <x:t>araçaiense</x:t>
   </x:si>
   <x:si>
-    <x:t>MARCIO GONZAGA DIAS DE OLIVEIRA</x:t>
+    <x:t xml:space="preserve">
+                MARCIO GONZAGA DIAS DE OLIVEIRA 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>35777-000</x:t>
@@ -1101,12 +1101,10 @@
     <x:t>36712</x:t>
   </x:si>
   <x:si>
-    <x:t>36.013
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16,10
-    hab/km²</x:t>
+    <x:t>36.013</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16,10</x:t>
   </x:si>
   <x:si>
     <x:t>3103405</x:t>
@@ -1115,7 +1113,9 @@
     <x:t>araçuaiense</x:t>
   </x:si>
   <x:si>
-    <x:t>TADEU BARBOSA DE OLIVEIRA</x:t>
+    <x:t xml:space="preserve">
+                TADEU BARBOSA DE OLIVEIRA 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>39600-000</x:t>
@@ -1127,12 +1127,10 @@
     <x:t>9401</x:t>
   </x:si>
   <x:si>
-    <x:t>7.883
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>32,11
-    hab/km²</x:t>
+    <x:t>7.883</x:t>
+  </x:si>
+  <x:si>
+    <x:t>32,11</x:t>
   </x:si>
   <x:si>
     <x:t>3103900</x:t>
@@ -1141,7 +1139,9 @@
     <x:t>araujense</x:t>
   </x:si>
   <x:si>
-    <x:t>GERALDO MAGELA DA SILVA</x:t>
+    <x:t xml:space="preserve">
+                GERALDO MAGELA DA SILVA 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>35603-000</x:t>
@@ -1153,12 +1153,10 @@
     <x:t>10883</x:t>
   </x:si>
   <x:si>
-    <x:t>9.509
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>58,38
-    hab/km²</x:t>
+    <x:t>9.509</x:t>
+  </x:si>
+  <x:si>
+    <x:t>58,38</x:t>
   </x:si>
   <x:si>
     <x:t>3104106</x:t>
@@ -1167,7 +1165,9 @@
     <x:t>arceburguense</x:t>
   </x:si>
   <x:si>
-    <x:t>GILSON PEREIRA DE MELLO</x:t>
+    <x:t xml:space="preserve">
+                GILSON PEREIRA DE MELLO 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>37820-000</x:t>
@@ -1179,12 +1179,10 @@
     <x:t>40380</x:t>
   </x:si>
   <x:si>
-    <x:t>36.597
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>71,78
-    hab/km²</x:t>
+    <x:t>36.597</x:t>
+  </x:si>
+  <x:si>
+    <x:t>71,78</x:t>
   </x:si>
   <x:si>
     <x:t>3104205</x:t>
@@ -1193,7 +1191,9 @@
     <x:t>arcoense</x:t>
   </x:si>
   <x:si>
-    <x:t>CLAUDENIR JOSÉ DE MELO</x:t>
+    <x:t xml:space="preserve">
+                CLAUDENIR JOSÉ DE MELO 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>35588-000</x:t>
@@ -1205,12 +1205,10 @@
     <x:t>25358</x:t>
   </x:si>
   <x:si>
-    <x:t>23.218
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8,59
-    hab/km²</x:t>
+    <x:t>23.218</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8,59</x:t>
   </x:si>
   <x:si>
     <x:t>3129509</x:t>
@@ -1219,7 +1217,9 @@
     <x:t>ibiaense</x:t>
   </x:si>
   <x:si>
-    <x:t>MARLENE APARECIDA DE SOUZA SILVA</x:t>
+    <x:t xml:space="preserve">
+                MARLENE APARECIDA DE SOUZA SILVA 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>38955-000</x:t>
@@ -1231,21 +1231,21 @@
     <x:t>5269</x:t>
   </x:si>
   <x:si>
-    <x:t>4.770
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19,60
-    hab/km²</x:t>
+    <x:t>4.770</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19,60</x:t>
   </x:si>
   <x:si>
     <x:t>3104452</x:t>
   </x:si>
   <x:si>
-    <x:t>aricanduvense ou aricanduvano</x:t>
-  </x:si>
-  <x:si>
-    <x:t>VALDEIR SANTOS COIMBRA</x:t>
+    <x:t>aricanduvenseouaricanduvano</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">
+                VALDEIR SANTOS COIMBRA 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>39678-000</x:t>
@@ -1257,12 +1257,10 @@
     <x:t>17862</x:t>
   </x:si>
   <x:si>
-    <x:t>17.674
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3,35
-    hab/km²</x:t>
+    <x:t>17.674</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,35</x:t>
   </x:si>
   <x:si>
     <x:t>3104502</x:t>
@@ -1271,7 +1269,9 @@
     <x:t>arinense</x:t>
   </x:si>
   <x:si>
-    <x:t>MARCÍLIO ÁLISSON FONSECA DE ALMEIDA</x:t>
+    <x:t xml:space="preserve">
+                MARCÍLIO ÁLISSON FONSECA DE ALMEIDA 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>38680-000</x:t>
@@ -1283,21 +1283,21 @@
     <x:t>94808</x:t>
   </x:si>
   <x:si>
-    <x:t>84.215
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>152,77
-    hab/km²</x:t>
+    <x:t>84.215</x:t>
+  </x:si>
+  <x:si>
+    <x:t>152,77</x:t>
   </x:si>
   <x:si>
     <x:t>3147105</x:t>
   </x:si>
   <x:si>
-    <x:t>pará-minense</x:t>
-  </x:si>
-  <x:si>
-    <x:t>ELIAS DINIZ</x:t>
+    <x:t>parminense</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">
+                ELIAS DINIZ 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>35665-000</x:t>
@@ -1309,21 +1309,21 @@
     <x:t>31364</x:t>
   </x:si>
   <x:si>
-    <x:t>27.856
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>92,02
-    hab/km²</x:t>
+    <x:t>27.856</x:t>
+  </x:si>
+  <x:si>
+    <x:t>92,02</x:t>
   </x:si>
   <x:si>
     <x:t>3140704</x:t>
   </x:si>
   <x:si>
-    <x:t>mateus-lemense</x:t>
-  </x:si>
-  <x:si>
-    <x:t>RENILTON RIBEIRO COELHO</x:t>
+    <x:t>mateuslemense</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">
+                RENILTON RIBEIRO COELHO 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>35672-000</x:t>
@@ -1338,12 +1338,10 @@
     <x:t>7131</x:t>
   </x:si>
   <x:si>
-    <x:t>6.830
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>4,95
-    hab/km²</x:t>
+    <x:t>6.830</x:t>
+  </x:si>
+  <x:si>
+    <x:t>4,95</x:t>
   </x:si>
   <x:si>
     <x:t>3121209</x:t>
@@ -1352,7 +1350,9 @@
     <x:t>delfinopolitano</x:t>
   </x:si>
   <x:si>
-    <x:t>SUELY ALVES FERREIRA LEMOS</x:t>
+    <x:t xml:space="preserve">
+                SUELY ALVES FERREIRA LEMOS 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>37915-000</x:t>
@@ -1364,12 +1364,10 @@
     <x:t>19199</x:t>
   </x:si>
   <x:si>
-    <x:t>18.307
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>24,39
-    hab/km²</x:t>
+    <x:t>18.307</x:t>
+  </x:si>
+  <x:si>
+    <x:t>24,39</x:t>
   </x:si>
   <x:si>
     <x:t>3104908</x:t>
@@ -1378,7 +1376,9 @@
     <x:t>baependiano</x:t>
   </x:si>
   <x:si>
-    <x:t>DOUGLAS STADUTO SOUZA</x:t>
+    <x:t xml:space="preserve">
+                DOUGLAS STADUTO SOUZA 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>37443-000</x:t>
@@ -1393,12 +1393,10 @@
     <x:t>337092</x:t>
   </x:si>
   <x:si>
-    <x:t>295.988
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>65,43
-    hab/km²</x:t>
+    <x:t>295.988</x:t>
+  </x:si>
+  <x:si>
+    <x:t>65,43</x:t>
   </x:si>
   <x:si>
     <x:t>3170107</x:t>
@@ -1407,7 +1405,9 @@
     <x:t>uberabense</x:t>
   </x:si>
   <x:si>
-    <x:t>ELISA GONÇALVES DE ARAÚJO</x:t>
+    <x:t xml:space="preserve">
+                ELISA GONÇALVES DE ARAÚJO 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>38101-000</x:t>
@@ -1416,6 +1416,26 @@
     <x:t>Uberaba</x:t>
   </x:si>
   <x:si>
+    <x:t>31497</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30.794</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16,99</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3141801</x:t>
+  </x:si>
+  <x:si>
+    <x:t>minasnovense</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">
+                AECIO GUEDES SOARES 
+            </x:t>
+  </x:si>
+  <x:si>
     <x:t>39652-000</x:t>
   </x:si>
   <x:si>
@@ -1431,12 +1451,10 @@
     <x:t>71551</x:t>
   </x:si>
   <x:si>
-    <x:t>60.271
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>66,20
-    hab/km²</x:t>
+    <x:t>60.271</x:t>
+  </x:si>
+  <x:si>
+    <x:t>66,20</x:t>
   </x:si>
   <x:si>
     <x:t>3124104</x:t>
@@ -1445,7 +1463,9 @@
     <x:t>esmeraldense</x:t>
   </x:si>
   <x:si>
-    <x:t>MARCELO NONATO FIGUEIREDO</x:t>
+    <x:t xml:space="preserve">
+                MARCELO NONATO FIGUEIREDO 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>32813-500</x:t>
@@ -1457,12 +1477,10 @@
     <x:t>23898</x:t>
   </x:si>
   <x:si>
-    <x:t>22.734
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>15,62
-    hab/km²</x:t>
+    <x:t>22.734</x:t>
+  </x:si>
+  <x:si>
+    <x:t>15,62</x:t>
   </x:si>
   <x:si>
     <x:t>3105103</x:t>
@@ -1471,7 +1489,9 @@
     <x:t>bambuiense</x:t>
   </x:si>
   <x:si>
-    <x:t>OLIVIO JOSÉ TEIXEIRA</x:t>
+    <x:t xml:space="preserve">
+                OLIVIO JOSÉ TEIXEIRA 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>38900-000</x:t>
@@ -1483,21 +1503,21 @@
     <x:t>5778</x:t>
   </x:si>
   <x:si>
-    <x:t>5.338
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>113,41
-    hab/km²</x:t>
+    <x:t>5.338</x:t>
+  </x:si>
+  <x:si>
+    <x:t>113,41</x:t>
   </x:si>
   <x:si>
     <x:t>3105301</x:t>
   </x:si>
   <x:si>
-    <x:t>bandeirante-do-sul</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EDERVAN LEANDRO DE FREITAS</x:t>
+    <x:t>bandeirantedosul</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">
+                EDERVAN LEANDRO DE FREITAS 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>37740-000</x:t>
@@ -1509,12 +1529,10 @@
     <x:t>61288</x:t>
   </x:si>
   <x:si>
-    <x:t>54.219
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>45,40
-    hab/km²</x:t>
+    <x:t>54.219</x:t>
+  </x:si>
+  <x:si>
+    <x:t>45,40</x:t>
   </x:si>
   <x:si>
     <x:t>3140001</x:t>
@@ -1523,7 +1541,9 @@
     <x:t>marianense</x:t>
   </x:si>
   <x:si>
-    <x:t>-</x:t>
+    <x:t xml:space="preserve">
+                - 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>35423-000</x:t>
@@ -1535,12 +1555,10 @@
     <x:t>265409</x:t>
   </x:si>
   <x:si>
-    <x:t>239.468
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>1.452,34
-    hab/km²</x:t>
+    <x:t>239.468</x:t>
+  </x:si>
+  <x:si>
+    <x:t>1.452,34</x:t>
   </x:si>
   <x:si>
     <x:t>3131307</x:t>
@@ -1549,7 +1567,9 @@
     <x:t>ipatinguense</x:t>
   </x:si>
   <x:si>
-    <x:t>GUSTAVO MORAIS NUNES</x:t>
+    <x:t xml:space="preserve">
+                GUSTAVO MORAIS NUNES 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>35165-000</x:t>
@@ -1561,12 +1581,10 @@
     <x:t>20883</x:t>
   </x:si>
   <x:si>
-    <x:t>19.064
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>55,15
-    hab/km²</x:t>
+    <x:t>19.064</x:t>
+  </x:si>
+  <x:si>
+    <x:t>55,15</x:t>
   </x:si>
   <x:si>
     <x:t>2927507</x:t>
@@ -1575,7 +1593,9 @@
     <x:t>barbarense</x:t>
   </x:si>
   <x:si>
-    <x:t>EDIFRANCIO DE JESUS OLIVEIRA</x:t>
+    <x:t xml:space="preserve">
+                EDIFRANCIO DE JESUS OLIVEIRA 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>35963-000</x:t>
@@ -1587,21 +1607,21 @@
     <x:t>5015</x:t>
   </x:si>
   <x:si>
-    <x:t>6.143
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>16,01
-    hab/km²</x:t>
+    <x:t>6.143</x:t>
+  </x:si>
+  <x:si>
+    <x:t>16,01</x:t>
   </x:si>
   <x:si>
     <x:t>3105707</x:t>
   </x:si>
   <x:si>
-    <x:t>barra-longuense</x:t>
-  </x:si>
-  <x:si>
-    <x:t>FERNANDO JOSÉ CARNEIRO MAGALHÃES</x:t>
+    <x:t>barralonguense</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">
+                FERNANDO JOSÉ CARNEIRO MAGALHÃES 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>35447-000</x:t>
@@ -1613,12 +1633,10 @@
     <x:t>27647</x:t>
   </x:si>
   <x:si>
-    <x:t>27.111
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>39,57
-    hab/km²</x:t>
+    <x:t>27.111</x:t>
+  </x:si>
+  <x:si>
+    <x:t>39,57</x:t>
   </x:si>
   <x:si>
     <x:t>3139607</x:t>
@@ -1627,7 +1645,9 @@
     <x:t>mantenense</x:t>
   </x:si>
   <x:si>
-    <x:t>JOÃO RUFINO SOBRINHO</x:t>
+    <x:t xml:space="preserve">
+                JOÃO RUFINO SOBRINHO 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>35295-000</x:t>
@@ -1642,12 +1662,10 @@
     <x:t>4965</x:t>
   </x:si>
   <x:si>
-    <x:t>5.102
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>17,73
-    hab/km²</x:t>
+    <x:t>5.102</x:t>
+  </x:si>
+  <x:si>
+    <x:t>17,73</x:t>
   </x:si>
   <x:si>
     <x:t>3115474</x:t>
@@ -1656,7 +1674,9 @@
     <x:t>catutiense</x:t>
   </x:si>
   <x:si>
-    <x:t>DELERMANDO DO NASCIMENTO FRANÇA</x:t>
+    <x:t xml:space="preserve">
+                DELERMANDO DO NASCIMENTO FRANÇA 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>39526-700</x:t>
@@ -1668,12 +1688,10 @@
     <x:t>72018</x:t>
   </x:si>
   <x:si>
-    <x:t>66.803
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>30,63
-    hab/km²</x:t>
+    <x:t>66.803</x:t>
+  </x:si>
+  <x:si>
+    <x:t>30,63</x:t>
   </x:si>
   <x:si>
     <x:t>3135100</x:t>
@@ -1682,7 +1700,9 @@
     <x:t>janaubense</x:t>
   </x:si>
   <x:si>
-    <x:t>JOSÉ APARECIDO MENDES SANTOS</x:t>
+    <x:t xml:space="preserve">
+                JOSÉ APARECIDO MENDES SANTOS 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>39449-300</x:t>
@@ -1700,21 +1720,21 @@
     <x:t>15890</x:t>
   </x:si>
   <x:si>
-    <x:t>15.024
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>3,87
-    hab/km²</x:t>
+    <x:t>15.024</x:t>
+  </x:si>
+  <x:si>
+    <x:t>3,87</x:t>
   </x:si>
   <x:si>
     <x:t>3127800</x:t>
   </x:si>
   <x:si>
-    <x:t>grão-mogolense</x:t>
-  </x:si>
-  <x:si>
-    <x:t>DIÊGO ANTONIO BRAGA FAGUNDES</x:t>
+    <x:t>gromogolense</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">
+                DIÊGO ANTONIO BRAGA FAGUNDES 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>39572-000</x:t>
@@ -1726,12 +1746,10 @@
     <x:t>32866</x:t>
   </x:si>
   <x:si>
-    <x:t>28.442
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>83,51
-    hab/km²</x:t>
+    <x:t>28.442</x:t>
+  </x:si>
+  <x:si>
+    <x:t>83,51</x:t>
   </x:si>
   <x:si>
     <x:t>3105400</x:t>
@@ -1740,7 +1758,9 @@
     <x:t>cocaiense</x:t>
   </x:si>
   <x:si>
-    <x:t>DÉCIO GERALDO DOS SANTOS</x:t>
+    <x:t xml:space="preserve">
+                DÉCIO GERALDO DOS SANTOS 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>35970-000</x:t>
@@ -1755,12 +1775,10 @@
     <x:t>3491</x:t>
   </x:si>
   <x:si>
-    <x:t>3.516
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5,53
-    hab/km²</x:t>
+    <x:t>3.516</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5,53</x:t>
   </x:si>
   <x:si>
     <x:t>3124708</x:t>
@@ -1769,7 +1787,9 @@
     <x:t>estrelense</x:t>
   </x:si>
   <x:si>
-    <x:t>WESLEY DANIEL RIBEIRO ARAUJO</x:t>
+    <x:t xml:space="preserve">
+                WESLEY DANIEL RIBEIRO ARAUJO 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>35615-000</x:t>
@@ -1781,21 +1801,21 @@
     <x:t>10262</x:t>
   </x:si>
   <x:si>
-    <x:t>10.004
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>91,66
-    hab/km²</x:t>
+    <x:t>10.004</x:t>
+  </x:si>
+  <x:si>
+    <x:t>91,66</x:t>
   </x:si>
   <x:si>
     <x:t>3106002</x:t>
   </x:si>
   <x:si>
-    <x:t>bela-vistano</x:t>
-  </x:si>
-  <x:si>
-    <x:t>SAMANTHA APARECIDA DE ÁVILA COSTA MAGALHÃES</x:t>
+    <x:t>belavistano</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">
+                SAMANTHA APARECIDA DE ÁVILA COSTA MAGALHÃES 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>35938-000</x:t>
@@ -1807,12 +1827,10 @@
     <x:t>3425</x:t>
   </x:si>
   <x:si>
-    <x:t>3.403
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8,66
-    hab/km²</x:t>
+    <x:t>3.403</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8,66</x:t>
   </x:si>
   <x:si>
     <x:t>3106101</x:t>
@@ -1821,7 +1839,9 @@
     <x:t>belmirense</x:t>
   </x:si>
   <x:si>
-    <x:t>JOSÉ PAULO DE OLIVEIRA FRANCO</x:t>
+    <x:t xml:space="preserve">
+                JOSÉ PAULO DE OLIVEIRA FRANCO 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>36126-000</x:t>
@@ -1833,21 +1853,21 @@
     <x:t>26994</x:t>
   </x:si>
   <x:si>
-    <x:t>23.397
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>69,86
-    hab/km²</x:t>
+    <x:t>23.397</x:t>
+  </x:si>
+  <x:si>
+    <x:t>69,86</x:t>
   </x:si>
   <x:si>
     <x:t>3106309</x:t>
   </x:si>
   <x:si>
-    <x:t>belo-orientino</x:t>
-  </x:si>
-  <x:si>
-    <x:t>HAMILTON ROMULO DE MENEZES CARVALHO</x:t>
+    <x:t>beloorientino</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">
+                HAMILTON ROMULO DE MENEZES CARVALHO 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>35195-000</x:t>
@@ -1859,21 +1879,21 @@
     <x:t>7719</x:t>
   </x:si>
   <x:si>
-    <x:t>7.536
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20,59
-    hab/km²</x:t>
+    <x:t>7.536</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20,59</x:t>
   </x:si>
   <x:si>
     <x:t>3106408</x:t>
   </x:si>
   <x:si>
-    <x:t>belo-valense</x:t>
-  </x:si>
-  <x:si>
-    <x:t>WALTENIR LIBERATO SOARES</x:t>
+    <x:t>belovalense</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">
+                WALTENIR LIBERATO SOARES 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>35473-000</x:t>
@@ -1885,12 +1905,10 @@
     <x:t>11872</x:t>
   </x:si>
   <x:si>
-    <x:t>12.300
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>20,95
-    hab/km²</x:t>
+    <x:t>12.300</x:t>
+  </x:si>
+  <x:si>
+    <x:t>20,95</x:t>
   </x:si>
   <x:si>
     <x:t>3106507</x:t>
@@ -1899,7 +1917,9 @@
     <x:t>berilense</x:t>
   </x:si>
   <x:si>
-    <x:t>ELANE LUIZ ALVES</x:t>
+    <x:t xml:space="preserve">
+                ELANE LUIZ ALVES 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>39640-000</x:t>
@@ -1911,12 +1931,10 @@
     <x:t>4764</x:t>
   </x:si>
   <x:si>
-    <x:t>4.370
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>8,94
-    hab/km²</x:t>
+    <x:t>4.370</x:t>
+  </x:si>
+  <x:si>
+    <x:t>8,94</x:t>
   </x:si>
   <x:si>
     <x:t>3106655</x:t>
@@ -1925,7 +1943,9 @@
     <x:t>berizalense</x:t>
   </x:si>
   <x:si>
-    <x:t>JOÃO CARLOS LUCAS LOPES</x:t>
+    <x:t xml:space="preserve">
+                JOÃO CARLOS LUCAS LOPES 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>39555-000</x:t>
@@ -1937,21 +1957,21 @@
     <x:t>23711</x:t>
   </x:si>
   <x:si>
-    <x:t>23.818
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>31,20
-    hab/km²</x:t>
+    <x:t>23.818</x:t>
+  </x:si>
+  <x:si>
+    <x:t>31,20</x:t>
   </x:si>
   <x:si>
     <x:t>3154002</x:t>
   </x:si>
   <x:si>
-    <x:t>raul-soarense</x:t>
-  </x:si>
-  <x:si>
-    <x:t>AMÉRICO DE ALMEIDA CÉZAR</x:t>
+    <x:t>raulsoarense</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">
+                AMÉRICO DE ALMEIDA CÉZAR 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>35352-000</x:t>
@@ -1963,12 +1983,10 @@
     <x:t>2498</x:t>
   </x:si>
   <x:si>
-    <x:t>2.630
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>5,73
-    hab/km²</x:t>
+    <x:t>2.630</x:t>
+  </x:si>
+  <x:si>
+    <x:t>5,73</x:t>
   </x:si>
   <x:si>
     <x:t>3107000</x:t>
@@ -1977,7 +1995,9 @@
     <x:t>biquinhense</x:t>
   </x:si>
   <x:si>
-    <x:t>ARISLEU FERREIRA PIRES</x:t>
+    <x:t xml:space="preserve">
+                ARISLEU FERREIRA PIRES 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>35621-000</x:t>
@@ -1989,12 +2009,10 @@
     <x:t>4852</x:t>
   </x:si>
   <x:si>
-    <x:t>5.395
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>22,84
-    hab/km²</x:t>
+    <x:t>5.395</x:t>
+  </x:si>
+  <x:si>
+    <x:t>22,84</x:t>
   </x:si>
   <x:si>
     <x:t>3135407</x:t>
@@ -2003,7 +2021,9 @@
     <x:t>jeceabense</x:t>
   </x:si>
   <x:si>
-    <x:t>JOSE DONIZETE ALMEIDA MAIA</x:t>
+    <x:t xml:space="preserve">
+                JOSE DONIZETE ALMEIDA MAIA 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>35497-000</x:t>
@@ -2021,12 +2041,10 @@
     <x:t>11576</x:t>
   </x:si>
   <x:si>
-    <x:t>10.692
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>51,16
-    hab/km²</x:t>
+    <x:t>10.692</x:t>
+  </x:si>
+  <x:si>
+    <x:t>51,16</x:t>
   </x:si>
   <x:si>
     <x:t>3131802</x:t>
@@ -2035,7 +2053,9 @@
     <x:t>itabirense</x:t>
   </x:si>
   <x:si>
-    <x:t>LUCAS COIMBRA DONADIA</x:t>
+    <x:t xml:space="preserve">
+                LUCAS COIMBRA DONADIA 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>35285-000</x:t>
@@ -2050,21 +2070,21 @@
     <x:t>105520</x:t>
   </x:si>
   <x:si>
-    <x:t>73.699
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>261,00
-    hab/km²</x:t>
+    <x:t>73.699</x:t>
+  </x:si>
+  <x:si>
+    <x:t>261,00</x:t>
   </x:si>
   <x:si>
     <x:t>3145208</x:t>
   </x:si>
   <x:si>
-    <x:t>nova-serranense</x:t>
-  </x:si>
-  <x:si>
-    <x:t>EUZEBIO RODRIGUES LAGO</x:t>
+    <x:t>novaserranense</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">
+                EUZEBIO RODRIGUES LAGO 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>35529-000</x:t>
@@ -2076,12 +2096,10 @@
     <x:t>84930</x:t>
   </x:si>
   <x:si>
-    <x:t>77.565
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>9,18
-    hab/km²</x:t>
+    <x:t>77.565</x:t>
+  </x:si>
+  <x:si>
+    <x:t>9,18</x:t>
   </x:si>
   <x:si>
     <x:t>3170404</x:t>
@@ -2090,7 +2108,9 @@
     <x:t>unaiense</x:t>
   </x:si>
   <x:si>
-    <x:t>JOSE GOMES BRANQUINHO</x:t>
+    <x:t xml:space="preserve">
+                JOSE GOMES BRANQUINHO 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>38621-000</x:t>
@@ -2102,21 +2122,21 @@
     <x:t>51028</x:t>
   </x:si>
   <x:si>
-    <x:t>45.624
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>37,28
-    hab/km²</x:t>
+    <x:t>45.624</x:t>
+  </x:si>
+  <x:si>
+    <x:t>37,28</x:t>
   </x:si>
   <x:si>
     <x:t>3107406</x:t>
   </x:si>
   <x:si>
-    <x:t>bom-despachense</x:t>
-  </x:si>
-  <x:si>
-    <x:t>BERTOLINO DA COSTA NETO</x:t>
+    <x:t>bomdespachense</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">
+                BERTOLINO DA COSTA NETO 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>35600-000</x:t>
@@ -2128,12 +2148,10 @@
     <x:t>19559</x:t>
   </x:si>
   <x:si>
-    <x:t>17.048
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>42,62
-    hab/km²</x:t>
+    <x:t>17.048</x:t>
+  </x:si>
+  <x:si>
+    <x:t>42,62</x:t>
   </x:si>
   <x:si>
     <x:t>3114501</x:t>
@@ -2142,7 +2160,9 @@
     <x:t>carmopolitano</x:t>
   </x:si>
   <x:si>
-    <x:t>JOSÉ OMAR PAOLINELLI</x:t>
+    <x:t xml:space="preserve">
+                JOSÉ OMAR PAOLINELLI 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>35535-000</x:t>
@@ -2154,21 +2174,21 @@
     <x:t>4244</x:t>
   </x:si>
   <x:si>
-    <x:t>3.887
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>18,66
-    hab/km²</x:t>
+    <x:t>3.887</x:t>
+  </x:si>
+  <x:si>
+    <x:t>18,66</x:t>
   </x:si>
   <x:si>
     <x:t>3107604</x:t>
   </x:si>
   <x:si>
-    <x:t>bom-jesuense</x:t>
-  </x:si>
-  <x:si>
-    <x:t>NEI ANDRÉ FREIRE</x:t>
+    <x:t>bomjesuense</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">
+                NEI ANDRÉ FREIRE 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>37948-000</x:t>
@@ -2180,12 +2200,10 @@
     <x:t>22693</x:t>
   </x:si>
   <x:si>
-    <x:t>20.012
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>43,90
-    hab/km²</x:t>
+    <x:t>20.012</x:t>
+  </x:si>
+  <x:si>
+    <x:t>43,90</x:t>
   </x:si>
   <x:si>
     <x:t>3114204</x:t>
@@ -2194,7 +2212,9 @@
     <x:t>cajuruense</x:t>
   </x:si>
   <x:si>
-    <x:t>EDSON DE SOUZA VILELA</x:t>
+    <x:t xml:space="preserve">
+                EDSON DE SOUZA VILELA 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>35559-000</x:t>
@@ -2206,12 +2226,10 @@
     <x:t>10345</x:t>
   </x:si>
   <x:si>
-    <x:t>10.291
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>74,15
-    hab/km²</x:t>
+    <x:t>10.291</x:t>
+  </x:si>
+  <x:si>
+    <x:t>74,15</x:t>
   </x:si>
   <x:si>
     <x:t>3170503</x:t>
@@ -2220,7 +2238,9 @@
     <x:t>urucaniense</x:t>
   </x:si>
   <x:si>
-    <x:t>JOSÉ MÁRCIO GOMES OSÓRIO</x:t>
+    <x:t xml:space="preserve">
+                JOSÉ MÁRCIO GOMES OSÓRIO 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>35381-000</x:t>
@@ -2232,18 +2252,18 @@
     <x:t>6133</x:t>
   </x:si>
   <x:si>
-    <x:t>5.491
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>28,07
-    hab/km²</x:t>
+    <x:t>5.491</x:t>
+  </x:si>
+  <x:si>
+    <x:t>28,07</x:t>
   </x:si>
   <x:si>
     <x:t>3107703</x:t>
   </x:si>
   <x:si>
-    <x:t>PEDRO DOS SANTOS MOREIRA</x:t>
+    <x:t xml:space="preserve">
+                PEDRO DOS SANTOS MOREIRA 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>35908-000</x:t>
@@ -2255,18 +2275,18 @@
     <x:t>14862</x:t>
   </x:si>
   <x:si>
-    <x:t>15.364
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>25,94
-    hab/km²</x:t>
+    <x:t>15.364</x:t>
+  </x:si>
+  <x:si>
+    <x:t>25,94</x:t>
   </x:si>
   <x:si>
     <x:t>3107802</x:t>
   </x:si>
   <x:si>
-    <x:t>ANIBAL BORGES</x:t>
+    <x:t xml:space="preserve">
+                ANIBAL BORGES 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>35340-000</x:t>
@@ -2278,21 +2298,21 @@
     <x:t>9664</x:t>
   </x:si>
   <x:si>
-    <x:t>8.920
-    pessoas</x:t>
-  </x:si>
-  <x:si>
-    <x:t>19,00
-    hab/km²</x:t>
+    <x:t>8.920</x:t>
+  </x:si>
+  <x:si>
+    <x:t>19,00</x:t>
   </x:si>
   <x:si>
     <x:t>3126901</x:t>
   </x:si>
   <x:si>
-    <x:t>frei-inocenciano</x:t>
-  </x:si>
-  <x:si>
-    <x:t>JIMMY DUTRA GOULART</x:t>
+    <x:t>freiinocenciano</x:t>
+  </x:si>
+  <x:si>
+    <x:t xml:space="preserve">
+                JIMMY DUTRA GOULART 
+            </x:t>
   </x:si>
   <x:si>
     <x:t>35112-800</x:t>
@@ -4307,31 +4327,31 @@
     </x:row>
     <x:row r="58" spans="1:9">
       <x:c r="A58" s="0" t="s">
-        <x:v>424</x:v>
+        <x:v>432</x:v>
       </x:c>
       <x:c r="B58" s="0" t="s">
-        <x:v>425</x:v>
+        <x:v>433</x:v>
       </x:c>
       <x:c r="C58" s="0" t="s">
-        <x:v>426</x:v>
+        <x:v>434</x:v>
       </x:c>
       <x:c r="D58" s="0" t="s">
-        <x:v>427</x:v>
+        <x:v>435</x:v>
       </x:c>
       <x:c r="E58" s="0" t="s">
-        <x:v>428</x:v>
+        <x:v>436</x:v>
       </x:c>
       <x:c r="F58" s="0" t="s">
-        <x:v>429</x:v>
+        <x:v>437</x:v>
       </x:c>
       <x:c r="G58" s="0" t="s">
         <x:v>57</x:v>
       </x:c>
       <x:c r="H58" s="0" t="s">
-        <x:v>432</x:v>
+        <x:v>438</x:v>
       </x:c>
       <x:c r="I58" s="0" t="s">
-        <x:v>433</x:v>
+        <x:v>439</x:v>
       </x:c>
     </x:row>
     <x:row r="59" spans="1:9">
@@ -4357,7 +4377,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="H59" s="0" t="s">
-        <x:v>434</x:v>
+        <x:v>440</x:v>
       </x:c>
       <x:c r="I59" s="0" t="s">
         <x:v>115</x:v>
@@ -4365,28 +4385,28 @@
     </x:row>
     <x:row r="60" spans="1:9">
       <x:c r="A60" s="0" t="s">
-        <x:v>108</x:v>
+        <x:v>197</x:v>
       </x:c>
       <x:c r="B60" s="0" t="s">
-        <x:v>109</x:v>
+        <x:v>198</x:v>
       </x:c>
       <x:c r="C60" s="0" t="s">
-        <x:v>110</x:v>
+        <x:v>199</x:v>
       </x:c>
       <x:c r="D60" s="0" t="s">
-        <x:v>111</x:v>
+        <x:v>200</x:v>
       </x:c>
       <x:c r="E60" s="0" t="s">
-        <x:v>112</x:v>
+        <x:v>201</x:v>
       </x:c>
       <x:c r="F60" s="0" t="s">
-        <x:v>113</x:v>
+        <x:v>202</x:v>
       </x:c>
       <x:c r="G60" s="0" t="s">
-        <x:v>57</x:v>
+        <x:v>15</x:v>
       </x:c>
       <x:c r="H60" s="0" t="s">
-        <x:v>435</x:v>
+        <x:v>441</x:v>
       </x:c>
       <x:c r="I60" s="0" t="s">
         <x:v>204</x:v>
@@ -4394,234 +4414,234 @@
     </x:row>
     <x:row r="61" spans="1:9">
       <x:c r="A61" s="0" t="s">
-        <x:v>436</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="B61" s="0" t="s">
-        <x:v>437</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="C61" s="0" t="s">
-        <x:v>438</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="D61" s="0" t="s">
-        <x:v>439</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="E61" s="0" t="s">
-        <x:v>440</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="F61" s="0" t="s">
-        <x:v>441</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="G61" s="0" t="s">
         <x:v>57</x:v>
       </x:c>
       <x:c r="H61" s="0" t="s">
-        <x:v>442</x:v>
+        <x:v>448</x:v>
       </x:c>
       <x:c r="I61" s="0" t="s">
-        <x:v>443</x:v>
+        <x:v>449</x:v>
       </x:c>
     </x:row>
     <x:row r="62" spans="1:9">
       <x:c r="A62" s="0" t="s">
-        <x:v>444</x:v>
+        <x:v>450</x:v>
       </x:c>
       <x:c r="B62" s="0" t="s">
-        <x:v>445</x:v>
+        <x:v>451</x:v>
       </x:c>
       <x:c r="C62" s="0" t="s">
-        <x:v>446</x:v>
+        <x:v>452</x:v>
       </x:c>
       <x:c r="D62" s="0" t="s">
-        <x:v>447</x:v>
+        <x:v>453</x:v>
       </x:c>
       <x:c r="E62" s="0" t="s">
-        <x:v>448</x:v>
+        <x:v>454</x:v>
       </x:c>
       <x:c r="F62" s="0" t="s">
-        <x:v>449</x:v>
+        <x:v>455</x:v>
       </x:c>
       <x:c r="G62" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="H62" s="0" t="s">
-        <x:v>450</x:v>
+        <x:v>456</x:v>
       </x:c>
       <x:c r="I62" s="0" t="s">
-        <x:v>451</x:v>
+        <x:v>457</x:v>
       </x:c>
     </x:row>
     <x:row r="63" spans="1:9">
       <x:c r="A63" s="0" t="s">
-        <x:v>452</x:v>
+        <x:v>458</x:v>
       </x:c>
       <x:c r="B63" s="0" t="s">
-        <x:v>453</x:v>
+        <x:v>459</x:v>
       </x:c>
       <x:c r="C63" s="0" t="s">
-        <x:v>454</x:v>
+        <x:v>460</x:v>
       </x:c>
       <x:c r="D63" s="0" t="s">
-        <x:v>455</x:v>
+        <x:v>461</x:v>
       </x:c>
       <x:c r="E63" s="0" t="s">
-        <x:v>456</x:v>
+        <x:v>462</x:v>
       </x:c>
       <x:c r="F63" s="0" t="s">
-        <x:v>457</x:v>
+        <x:v>463</x:v>
       </x:c>
       <x:c r="G63" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="H63" s="0" t="s">
-        <x:v>458</x:v>
+        <x:v>464</x:v>
       </x:c>
       <x:c r="I63" s="0" t="s">
-        <x:v>459</x:v>
+        <x:v>465</x:v>
       </x:c>
     </x:row>
     <x:row r="64" spans="1:9">
       <x:c r="A64" s="0" t="s">
-        <x:v>460</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="B64" s="0" t="s">
-        <x:v>461</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="C64" s="0" t="s">
-        <x:v>462</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="D64" s="0" t="s">
-        <x:v>463</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="E64" s="0" t="s">
-        <x:v>464</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="F64" s="0" t="s">
-        <x:v>465</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="G64" s="0" t="s">
         <x:v>57</x:v>
       </x:c>
       <x:c r="H64" s="0" t="s">
-        <x:v>466</x:v>
+        <x:v>472</x:v>
       </x:c>
       <x:c r="I64" s="0" t="s">
-        <x:v>467</x:v>
+        <x:v>473</x:v>
       </x:c>
     </x:row>
     <x:row r="65" spans="1:9">
       <x:c r="A65" s="0" t="s">
-        <x:v>468</x:v>
+        <x:v>474</x:v>
       </x:c>
       <x:c r="B65" s="0" t="s">
-        <x:v>469</x:v>
+        <x:v>475</x:v>
       </x:c>
       <x:c r="C65" s="0" t="s">
-        <x:v>470</x:v>
+        <x:v>476</x:v>
       </x:c>
       <x:c r="D65" s="0" t="s">
-        <x:v>471</x:v>
+        <x:v>477</x:v>
       </x:c>
       <x:c r="E65" s="0" t="s">
-        <x:v>472</x:v>
+        <x:v>478</x:v>
       </x:c>
       <x:c r="F65" s="0" t="s">
-        <x:v>473</x:v>
+        <x:v>479</x:v>
       </x:c>
       <x:c r="G65" s="0" t="s">
         <x:v>57</x:v>
       </x:c>
       <x:c r="H65" s="0" t="s">
-        <x:v>474</x:v>
+        <x:v>480</x:v>
       </x:c>
       <x:c r="I65" s="0" t="s">
-        <x:v>475</x:v>
+        <x:v>481</x:v>
       </x:c>
     </x:row>
     <x:row r="66" spans="1:9">
       <x:c r="A66" s="0" t="s">
-        <x:v>476</x:v>
+        <x:v>482</x:v>
       </x:c>
       <x:c r="B66" s="0" t="s">
-        <x:v>477</x:v>
+        <x:v>483</x:v>
       </x:c>
       <x:c r="C66" s="0" t="s">
-        <x:v>478</x:v>
+        <x:v>484</x:v>
       </x:c>
       <x:c r="D66" s="0" t="s">
-        <x:v>479</x:v>
+        <x:v>485</x:v>
       </x:c>
       <x:c r="E66" s="0" t="s">
-        <x:v>480</x:v>
+        <x:v>486</x:v>
       </x:c>
       <x:c r="F66" s="0" t="s">
-        <x:v>481</x:v>
+        <x:v>487</x:v>
       </x:c>
       <x:c r="G66" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="H66" s="0" t="s">
-        <x:v>482</x:v>
+        <x:v>488</x:v>
       </x:c>
       <x:c r="I66" s="0" t="s">
-        <x:v>483</x:v>
+        <x:v>489</x:v>
       </x:c>
     </x:row>
     <x:row r="67" spans="1:9">
       <x:c r="A67" s="0" t="s">
-        <x:v>484</x:v>
+        <x:v>490</x:v>
       </x:c>
       <x:c r="B67" s="0" t="s">
-        <x:v>485</x:v>
+        <x:v>491</x:v>
       </x:c>
       <x:c r="C67" s="0" t="s">
-        <x:v>486</x:v>
+        <x:v>492</x:v>
       </x:c>
       <x:c r="D67" s="0" t="s">
-        <x:v>487</x:v>
+        <x:v>493</x:v>
       </x:c>
       <x:c r="E67" s="0" t="s">
-        <x:v>488</x:v>
+        <x:v>494</x:v>
       </x:c>
       <x:c r="F67" s="0" t="s">
-        <x:v>489</x:v>
+        <x:v>495</x:v>
       </x:c>
       <x:c r="G67" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="H67" s="0" t="s">
-        <x:v>490</x:v>
+        <x:v>496</x:v>
       </x:c>
       <x:c r="I67" s="0" t="s">
-        <x:v>491</x:v>
+        <x:v>497</x:v>
       </x:c>
     </x:row>
     <x:row r="68" spans="1:9">
       <x:c r="A68" s="0" t="s">
-        <x:v>492</x:v>
+        <x:v>498</x:v>
       </x:c>
       <x:c r="B68" s="0" t="s">
-        <x:v>493</x:v>
+        <x:v>499</x:v>
       </x:c>
       <x:c r="C68" s="0" t="s">
-        <x:v>494</x:v>
+        <x:v>500</x:v>
       </x:c>
       <x:c r="D68" s="0" t="s">
-        <x:v>495</x:v>
+        <x:v>501</x:v>
       </x:c>
       <x:c r="E68" s="0" t="s">
-        <x:v>496</x:v>
+        <x:v>502</x:v>
       </x:c>
       <x:c r="F68" s="0" t="s">
-        <x:v>497</x:v>
+        <x:v>503</x:v>
       </x:c>
       <x:c r="G68" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="H68" s="0" t="s">
-        <x:v>498</x:v>
+        <x:v>504</x:v>
       </x:c>
       <x:c r="I68" s="0" t="s">
-        <x:v>499</x:v>
+        <x:v>505</x:v>
       </x:c>
     </x:row>
     <x:row r="69" spans="1:9">
@@ -4647,7 +4667,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="H69" s="0" t="s">
-        <x:v>500</x:v>
+        <x:v>506</x:v>
       </x:c>
       <x:c r="I69" s="0" t="s">
         <x:v>123</x:v>
@@ -4655,60 +4675,60 @@
     </x:row>
     <x:row r="70" spans="1:9">
       <x:c r="A70" s="0" t="s">
-        <x:v>501</x:v>
+        <x:v>507</x:v>
       </x:c>
       <x:c r="B70" s="0" t="s">
-        <x:v>502</x:v>
+        <x:v>508</x:v>
       </x:c>
       <x:c r="C70" s="0" t="s">
-        <x:v>503</x:v>
+        <x:v>509</x:v>
       </x:c>
       <x:c r="D70" s="0" t="s">
-        <x:v>504</x:v>
+        <x:v>510</x:v>
       </x:c>
       <x:c r="E70" s="0" t="s">
-        <x:v>505</x:v>
+        <x:v>511</x:v>
       </x:c>
       <x:c r="F70" s="0" t="s">
-        <x:v>506</x:v>
+        <x:v>512</x:v>
       </x:c>
       <x:c r="G70" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="H70" s="0" t="s">
-        <x:v>507</x:v>
+        <x:v>513</x:v>
       </x:c>
       <x:c r="I70" s="0" t="s">
-        <x:v>508</x:v>
+        <x:v>514</x:v>
       </x:c>
     </x:row>
     <x:row r="71" spans="1:9">
       <x:c r="A71" s="0" t="s">
-        <x:v>509</x:v>
+        <x:v>515</x:v>
       </x:c>
       <x:c r="B71" s="0" t="s">
-        <x:v>510</x:v>
+        <x:v>516</x:v>
       </x:c>
       <x:c r="C71" s="0" t="s">
-        <x:v>511</x:v>
+        <x:v>517</x:v>
       </x:c>
       <x:c r="D71" s="0" t="s">
-        <x:v>512</x:v>
+        <x:v>518</x:v>
       </x:c>
       <x:c r="E71" s="0" t="s">
-        <x:v>513</x:v>
+        <x:v>519</x:v>
       </x:c>
       <x:c r="F71" s="0" t="s">
-        <x:v>514</x:v>
+        <x:v>520</x:v>
       </x:c>
       <x:c r="G71" s="0" t="s">
         <x:v>57</x:v>
       </x:c>
       <x:c r="H71" s="0" t="s">
-        <x:v>515</x:v>
+        <x:v>521</x:v>
       </x:c>
       <x:c r="I71" s="0" t="s">
-        <x:v>516</x:v>
+        <x:v>522</x:v>
       </x:c>
     </x:row>
     <x:row r="72" spans="1:9">
@@ -4734,7 +4754,7 @@
         <x:v>24</x:v>
       </x:c>
       <x:c r="H72" s="0" t="s">
-        <x:v>517</x:v>
+        <x:v>523</x:v>
       </x:c>
       <x:c r="I72" s="0" t="s">
         <x:v>196</x:v>
@@ -4742,89 +4762,89 @@
     </x:row>
     <x:row r="73" spans="1:9">
       <x:c r="A73" s="0" t="s">
-        <x:v>460</x:v>
+        <x:v>466</x:v>
       </x:c>
       <x:c r="B73" s="0" t="s">
-        <x:v>461</x:v>
+        <x:v>467</x:v>
       </x:c>
       <x:c r="C73" s="0" t="s">
-        <x:v>462</x:v>
+        <x:v>468</x:v>
       </x:c>
       <x:c r="D73" s="0" t="s">
-        <x:v>463</x:v>
+        <x:v>469</x:v>
       </x:c>
       <x:c r="E73" s="0" t="s">
-        <x:v>464</x:v>
+        <x:v>470</x:v>
       </x:c>
       <x:c r="F73" s="0" t="s">
-        <x:v>465</x:v>
+        <x:v>471</x:v>
       </x:c>
       <x:c r="G73" s="0" t="s">
         <x:v>57</x:v>
       </x:c>
       <x:c r="H73" s="0" t="s">
-        <x:v>518</x:v>
+        <x:v>524</x:v>
       </x:c>
       <x:c r="I73" s="0" t="s">
-        <x:v>467</x:v>
+        <x:v>473</x:v>
       </x:c>
     </x:row>
     <x:row r="74" spans="1:9">
       <x:c r="A74" s="0" t="s">
-        <x:v>519</x:v>
+        <x:v>525</x:v>
       </x:c>
       <x:c r="B74" s="0" t="s">
-        <x:v>520</x:v>
+        <x:v>526</x:v>
       </x:c>
       <x:c r="C74" s="0" t="s">
-        <x:v>521</x:v>
+        <x:v>527</x:v>
       </x:c>
       <x:c r="D74" s="0" t="s">
-        <x:v>522</x:v>
+        <x:v>528</x:v>
       </x:c>
       <x:c r="E74" s="0" t="s">
-        <x:v>523</x:v>
+        <x:v>529</x:v>
       </x:c>
       <x:c r="F74" s="0" t="s">
-        <x:v>524</x:v>
+        <x:v>530</x:v>
       </x:c>
       <x:c r="G74" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="H74" s="0" t="s">
-        <x:v>525</x:v>
+        <x:v>531</x:v>
       </x:c>
       <x:c r="I74" s="0" t="s">
-        <x:v>526</x:v>
+        <x:v>532</x:v>
       </x:c>
     </x:row>
     <x:row r="75" spans="1:9">
       <x:c r="A75" s="0" t="s">
-        <x:v>527</x:v>
+        <x:v>533</x:v>
       </x:c>
       <x:c r="B75" s="0" t="s">
-        <x:v>528</x:v>
+        <x:v>534</x:v>
       </x:c>
       <x:c r="C75" s="0" t="s">
-        <x:v>529</x:v>
+        <x:v>535</x:v>
       </x:c>
       <x:c r="D75" s="0" t="s">
-        <x:v>530</x:v>
+        <x:v>536</x:v>
       </x:c>
       <x:c r="E75" s="0" t="s">
-        <x:v>531</x:v>
+        <x:v>537</x:v>
       </x:c>
       <x:c r="F75" s="0" t="s">
-        <x:v>532</x:v>
+        <x:v>538</x:v>
       </x:c>
       <x:c r="G75" s="0" t="s">
         <x:v>57</x:v>
       </x:c>
       <x:c r="H75" s="0" t="s">
-        <x:v>533</x:v>
+        <x:v>539</x:v>
       </x:c>
       <x:c r="I75" s="0" t="s">
-        <x:v>534</x:v>
+        <x:v>540</x:v>
       </x:c>
     </x:row>
     <x:row r="76" spans="1:9">
@@ -4850,7 +4870,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="H76" s="0" t="s">
-        <x:v>535</x:v>
+        <x:v>541</x:v>
       </x:c>
       <x:c r="I76" s="0" t="s">
         <x:v>59</x:v>
@@ -4858,292 +4878,292 @@
     </x:row>
     <x:row r="77" spans="1:9">
       <x:c r="A77" s="0" t="s">
-        <x:v>536</x:v>
+        <x:v>542</x:v>
       </x:c>
       <x:c r="B77" s="0" t="s">
-        <x:v>537</x:v>
+        <x:v>543</x:v>
       </x:c>
       <x:c r="C77" s="0" t="s">
-        <x:v>538</x:v>
+        <x:v>544</x:v>
       </x:c>
       <x:c r="D77" s="0" t="s">
-        <x:v>539</x:v>
+        <x:v>545</x:v>
       </x:c>
       <x:c r="E77" s="0" t="s">
-        <x:v>540</x:v>
+        <x:v>546</x:v>
       </x:c>
       <x:c r="F77" s="0" t="s">
-        <x:v>541</x:v>
+        <x:v>547</x:v>
       </x:c>
       <x:c r="G77" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="H77" s="0" t="s">
-        <x:v>542</x:v>
+        <x:v>548</x:v>
       </x:c>
       <x:c r="I77" s="0" t="s">
-        <x:v>543</x:v>
+        <x:v>549</x:v>
       </x:c>
     </x:row>
     <x:row r="78" spans="1:9">
       <x:c r="A78" s="0" t="s">
-        <x:v>544</x:v>
+        <x:v>550</x:v>
       </x:c>
       <x:c r="B78" s="0" t="s">
-        <x:v>545</x:v>
+        <x:v>551</x:v>
       </x:c>
       <x:c r="C78" s="0" t="s">
-        <x:v>546</x:v>
+        <x:v>552</x:v>
       </x:c>
       <x:c r="D78" s="0" t="s">
-        <x:v>547</x:v>
+        <x:v>553</x:v>
       </x:c>
       <x:c r="E78" s="0" t="s">
-        <x:v>548</x:v>
+        <x:v>554</x:v>
       </x:c>
       <x:c r="F78" s="0" t="s">
-        <x:v>549</x:v>
+        <x:v>555</x:v>
       </x:c>
       <x:c r="G78" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="H78" s="0" t="s">
-        <x:v>550</x:v>
+        <x:v>556</x:v>
       </x:c>
       <x:c r="I78" s="0" t="s">
-        <x:v>551</x:v>
+        <x:v>557</x:v>
       </x:c>
     </x:row>
     <x:row r="79" spans="1:9">
       <x:c r="A79" s="0" t="s">
-        <x:v>552</x:v>
+        <x:v>558</x:v>
       </x:c>
       <x:c r="B79" s="0" t="s">
-        <x:v>553</x:v>
+        <x:v>559</x:v>
       </x:c>
       <x:c r="C79" s="0" t="s">
-        <x:v>554</x:v>
+        <x:v>560</x:v>
       </x:c>
       <x:c r="D79" s="0" t="s">
-        <x:v>555</x:v>
+        <x:v>561</x:v>
       </x:c>
       <x:c r="E79" s="0" t="s">
-        <x:v>556</x:v>
+        <x:v>562</x:v>
       </x:c>
       <x:c r="F79" s="0" t="s">
-        <x:v>557</x:v>
+        <x:v>563</x:v>
       </x:c>
       <x:c r="G79" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="H79" s="0" t="s">
-        <x:v>558</x:v>
+        <x:v>564</x:v>
       </x:c>
       <x:c r="I79" s="0" t="s">
-        <x:v>559</x:v>
+        <x:v>565</x:v>
       </x:c>
     </x:row>
     <x:row r="80" spans="1:9">
       <x:c r="A80" s="0" t="s">
-        <x:v>560</x:v>
+        <x:v>566</x:v>
       </x:c>
       <x:c r="B80" s="0" t="s">
-        <x:v>561</x:v>
+        <x:v>567</x:v>
       </x:c>
       <x:c r="C80" s="0" t="s">
-        <x:v>562</x:v>
+        <x:v>568</x:v>
       </x:c>
       <x:c r="D80" s="0" t="s">
-        <x:v>563</x:v>
+        <x:v>569</x:v>
       </x:c>
       <x:c r="E80" s="0" t="s">
-        <x:v>564</x:v>
+        <x:v>570</x:v>
       </x:c>
       <x:c r="F80" s="0" t="s">
-        <x:v>565</x:v>
+        <x:v>571</x:v>
       </x:c>
       <x:c r="G80" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="H80" s="0" t="s">
-        <x:v>566</x:v>
+        <x:v>572</x:v>
       </x:c>
       <x:c r="I80" s="0" t="s">
-        <x:v>567</x:v>
+        <x:v>573</x:v>
       </x:c>
     </x:row>
     <x:row r="81" spans="1:9">
       <x:c r="A81" s="0" t="s">
-        <x:v>568</x:v>
+        <x:v>574</x:v>
       </x:c>
       <x:c r="B81" s="0" t="s">
-        <x:v>569</x:v>
+        <x:v>575</x:v>
       </x:c>
       <x:c r="C81" s="0" t="s">
-        <x:v>570</x:v>
+        <x:v>576</x:v>
       </x:c>
       <x:c r="D81" s="0" t="s">
-        <x:v>571</x:v>
+        <x:v>577</x:v>
       </x:c>
       <x:c r="E81" s="0" t="s">
-        <x:v>572</x:v>
+        <x:v>578</x:v>
       </x:c>
       <x:c r="F81" s="0" t="s">
-        <x:v>573</x:v>
+        <x:v>579</x:v>
       </x:c>
       <x:c r="G81" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="H81" s="0" t="s">
-        <x:v>574</x:v>
+        <x:v>580</x:v>
       </x:c>
       <x:c r="I81" s="0" t="s">
-        <x:v>575</x:v>
+        <x:v>581</x:v>
       </x:c>
     </x:row>
     <x:row r="82" spans="1:9">
       <x:c r="A82" s="0" t="s">
-        <x:v>576</x:v>
+        <x:v>582</x:v>
       </x:c>
       <x:c r="B82" s="0" t="s">
-        <x:v>577</x:v>
+        <x:v>583</x:v>
       </x:c>
       <x:c r="C82" s="0" t="s">
-        <x:v>578</x:v>
+        <x:v>584</x:v>
       </x:c>
       <x:c r="D82" s="0" t="s">
-        <x:v>579</x:v>
+        <x:v>585</x:v>
       </x:c>
       <x:c r="E82" s="0" t="s">
-        <x:v>580</x:v>
+        <x:v>586</x:v>
       </x:c>
       <x:c r="F82" s="0" t="s">
-        <x:v>581</x:v>
+        <x:v>587</x:v>
       </x:c>
       <x:c r="G82" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="H82" s="0" t="s">
-        <x:v>582</x:v>
+        <x:v>588</x:v>
       </x:c>
       <x:c r="I82" s="0" t="s">
-        <x:v>583</x:v>
+        <x:v>589</x:v>
       </x:c>
     </x:row>
     <x:row r="83" spans="1:9">
       <x:c r="A83" s="0" t="s">
-        <x:v>584</x:v>
+        <x:v>590</x:v>
       </x:c>
       <x:c r="B83" s="0" t="s">
-        <x:v>585</x:v>
+        <x:v>591</x:v>
       </x:c>
       <x:c r="C83" s="0" t="s">
-        <x:v>586</x:v>
+        <x:v>592</x:v>
       </x:c>
       <x:c r="D83" s="0" t="s">
-        <x:v>587</x:v>
+        <x:v>593</x:v>
       </x:c>
       <x:c r="E83" s="0" t="s">
-        <x:v>588</x:v>
+        <x:v>594</x:v>
       </x:c>
       <x:c r="F83" s="0" t="s">
-        <x:v>589</x:v>
+        <x:v>595</x:v>
       </x:c>
       <x:c r="G83" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="H83" s="0" t="s">
-        <x:v>590</x:v>
+        <x:v>596</x:v>
       </x:c>
       <x:c r="I83" s="0" t="s">
-        <x:v>591</x:v>
+        <x:v>597</x:v>
       </x:c>
     </x:row>
     <x:row r="84" spans="1:9">
       <x:c r="A84" s="0" t="s">
-        <x:v>592</x:v>
+        <x:v>598</x:v>
       </x:c>
       <x:c r="B84" s="0" t="s">
-        <x:v>593</x:v>
+        <x:v>599</x:v>
       </x:c>
       <x:c r="C84" s="0" t="s">
-        <x:v>594</x:v>
+        <x:v>600</x:v>
       </x:c>
       <x:c r="D84" s="0" t="s">
-        <x:v>595</x:v>
+        <x:v>601</x:v>
       </x:c>
       <x:c r="E84" s="0" t="s">
-        <x:v>596</x:v>
+        <x:v>602</x:v>
       </x:c>
       <x:c r="F84" s="0" t="s">
-        <x:v>597</x:v>
+        <x:v>603</x:v>
       </x:c>
       <x:c r="G84" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="H84" s="0" t="s">
-        <x:v>598</x:v>
+        <x:v>604</x:v>
       </x:c>
       <x:c r="I84" s="0" t="s">
-        <x:v>599</x:v>
+        <x:v>605</x:v>
       </x:c>
     </x:row>
     <x:row r="85" spans="1:9">
       <x:c r="A85" s="0" t="s">
-        <x:v>600</x:v>
+        <x:v>606</x:v>
       </x:c>
       <x:c r="B85" s="0" t="s">
-        <x:v>601</x:v>
+        <x:v>607</x:v>
       </x:c>
       <x:c r="C85" s="0" t="s">
-        <x:v>602</x:v>
+        <x:v>608</x:v>
       </x:c>
       <x:c r="D85" s="0" t="s">
-        <x:v>603</x:v>
+        <x:v>609</x:v>
       </x:c>
       <x:c r="E85" s="0" t="s">
-        <x:v>604</x:v>
+        <x:v>610</x:v>
       </x:c>
       <x:c r="F85" s="0" t="s">
-        <x:v>605</x:v>
+        <x:v>611</x:v>
       </x:c>
       <x:c r="G85" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="H85" s="0" t="s">
-        <x:v>606</x:v>
+        <x:v>612</x:v>
       </x:c>
       <x:c r="I85" s="0" t="s">
-        <x:v>607</x:v>
+        <x:v>613</x:v>
       </x:c>
     </x:row>
     <x:row r="86" spans="1:9">
       <x:c r="A86" s="0" t="s">
-        <x:v>608</x:v>
+        <x:v>614</x:v>
       </x:c>
       <x:c r="B86" s="0" t="s">
-        <x:v>609</x:v>
+        <x:v>615</x:v>
       </x:c>
       <x:c r="C86" s="0" t="s">
-        <x:v>610</x:v>
+        <x:v>616</x:v>
       </x:c>
       <x:c r="D86" s="0" t="s">
-        <x:v>611</x:v>
+        <x:v>617</x:v>
       </x:c>
       <x:c r="E86" s="0" t="s">
-        <x:v>612</x:v>
+        <x:v>618</x:v>
       </x:c>
       <x:c r="F86" s="0" t="s">
-        <x:v>613</x:v>
+        <x:v>619</x:v>
       </x:c>
       <x:c r="G86" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="H86" s="0" t="s">
-        <x:v>614</x:v>
+        <x:v>620</x:v>
       </x:c>
       <x:c r="I86" s="0" t="s">
-        <x:v>615</x:v>
+        <x:v>621</x:v>
       </x:c>
     </x:row>
     <x:row r="87" spans="1:9">
@@ -5169,7 +5189,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="H87" s="0" t="s">
-        <x:v>616</x:v>
+        <x:v>622</x:v>
       </x:c>
       <x:c r="I87" s="0" t="s">
         <x:v>285</x:v>
@@ -5198,7 +5218,7 @@
         <x:v>57</x:v>
       </x:c>
       <x:c r="H88" s="0" t="s">
-        <x:v>617</x:v>
+        <x:v>623</x:v>
       </x:c>
       <x:c r="I88" s="0" t="s">
         <x:v>115</x:v>
@@ -5206,350 +5226,350 @@
     </x:row>
     <x:row r="89" spans="1:9">
       <x:c r="A89" s="0" t="s">
-        <x:v>618</x:v>
+        <x:v>624</x:v>
       </x:c>
       <x:c r="B89" s="0" t="s">
-        <x:v>619</x:v>
+        <x:v>625</x:v>
       </x:c>
       <x:c r="C89" s="0" t="s">
-        <x:v>620</x:v>
+        <x:v>626</x:v>
       </x:c>
       <x:c r="D89" s="0" t="s">
-        <x:v>621</x:v>
+        <x:v>627</x:v>
       </x:c>
       <x:c r="E89" s="0" t="s">
-        <x:v>622</x:v>
+        <x:v>628</x:v>
       </x:c>
       <x:c r="F89" s="0" t="s">
-        <x:v>623</x:v>
+        <x:v>629</x:v>
       </x:c>
       <x:c r="G89" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="H89" s="0" t="s">
-        <x:v>624</x:v>
+        <x:v>630</x:v>
       </x:c>
       <x:c r="I89" s="0" t="s">
-        <x:v>625</x:v>
+        <x:v>631</x:v>
       </x:c>
     </x:row>
     <x:row r="90" spans="1:9">
       <x:c r="A90" s="0" t="s">
-        <x:v>436</x:v>
+        <x:v>442</x:v>
       </x:c>
       <x:c r="B90" s="0" t="s">
-        <x:v>437</x:v>
+        <x:v>443</x:v>
       </x:c>
       <x:c r="C90" s="0" t="s">
-        <x:v>438</x:v>
+        <x:v>444</x:v>
       </x:c>
       <x:c r="D90" s="0" t="s">
-        <x:v>439</x:v>
+        <x:v>445</x:v>
       </x:c>
       <x:c r="E90" s="0" t="s">
-        <x:v>440</x:v>
+        <x:v>446</x:v>
       </x:c>
       <x:c r="F90" s="0" t="s">
-        <x:v>441</x:v>
+        <x:v>447</x:v>
       </x:c>
       <x:c r="G90" s="0" t="s">
         <x:v>57</x:v>
       </x:c>
       <x:c r="H90" s="0" t="s">
-        <x:v>626</x:v>
+        <x:v>632</x:v>
       </x:c>
       <x:c r="I90" s="0" t="s">
-        <x:v>443</x:v>
+        <x:v>449</x:v>
       </x:c>
     </x:row>
     <x:row r="91" spans="1:9">
       <x:c r="A91" s="0" t="s">
-        <x:v>627</x:v>
+        <x:v>633</x:v>
       </x:c>
       <x:c r="B91" s="0" t="s">
-        <x:v>628</x:v>
+        <x:v>634</x:v>
       </x:c>
       <x:c r="C91" s="0" t="s">
-        <x:v>629</x:v>
+        <x:v>635</x:v>
       </x:c>
       <x:c r="D91" s="0" t="s">
-        <x:v>630</x:v>
+        <x:v>636</x:v>
       </x:c>
       <x:c r="E91" s="0" t="s">
-        <x:v>631</x:v>
+        <x:v>637</x:v>
       </x:c>
       <x:c r="F91" s="0" t="s">
-        <x:v>632</x:v>
+        <x:v>638</x:v>
       </x:c>
       <x:c r="G91" s="0" t="s">
         <x:v>57</x:v>
       </x:c>
       <x:c r="H91" s="0" t="s">
-        <x:v>633</x:v>
+        <x:v>639</x:v>
       </x:c>
       <x:c r="I91" s="0" t="s">
-        <x:v>634</x:v>
+        <x:v>640</x:v>
       </x:c>
     </x:row>
     <x:row r="92" spans="1:9">
       <x:c r="A92" s="0" t="s">
-        <x:v>635</x:v>
+        <x:v>641</x:v>
       </x:c>
       <x:c r="B92" s="0" t="s">
-        <x:v>636</x:v>
+        <x:v>642</x:v>
       </x:c>
       <x:c r="C92" s="0" t="s">
-        <x:v>637</x:v>
+        <x:v>643</x:v>
       </x:c>
       <x:c r="D92" s="0" t="s">
-        <x:v>638</x:v>
+        <x:v>644</x:v>
       </x:c>
       <x:c r="E92" s="0" t="s">
-        <x:v>639</x:v>
+        <x:v>645</x:v>
       </x:c>
       <x:c r="F92" s="0" t="s">
-        <x:v>640</x:v>
+        <x:v>646</x:v>
       </x:c>
       <x:c r="G92" s="0" t="s">
         <x:v>57</x:v>
       </x:c>
       <x:c r="H92" s="0" t="s">
-        <x:v>641</x:v>
+        <x:v>647</x:v>
       </x:c>
       <x:c r="I92" s="0" t="s">
-        <x:v>642</x:v>
+        <x:v>648</x:v>
       </x:c>
     </x:row>
     <x:row r="93" spans="1:9">
       <x:c r="A93" s="0" t="s">
-        <x:v>643</x:v>
+        <x:v>649</x:v>
       </x:c>
       <x:c r="B93" s="0" t="s">
-        <x:v>644</x:v>
+        <x:v>650</x:v>
       </x:c>
       <x:c r="C93" s="0" t="s">
-        <x:v>645</x:v>
+        <x:v>651</x:v>
       </x:c>
       <x:c r="D93" s="0" t="s">
-        <x:v>646</x:v>
+        <x:v>652</x:v>
       </x:c>
       <x:c r="E93" s="0" t="s">
-        <x:v>647</x:v>
+        <x:v>653</x:v>
       </x:c>
       <x:c r="F93" s="0" t="s">
-        <x:v>648</x:v>
+        <x:v>654</x:v>
       </x:c>
       <x:c r="G93" s="0" t="s">
         <x:v>57</x:v>
       </x:c>
       <x:c r="H93" s="0" t="s">
-        <x:v>649</x:v>
+        <x:v>655</x:v>
       </x:c>
       <x:c r="I93" s="0" t="s">
-        <x:v>650</x:v>
+        <x:v>656</x:v>
       </x:c>
     </x:row>
     <x:row r="94" spans="1:9">
       <x:c r="A94" s="0" t="s">
-        <x:v>651</x:v>
+        <x:v>657</x:v>
       </x:c>
       <x:c r="B94" s="0" t="s">
-        <x:v>652</x:v>
+        <x:v>658</x:v>
       </x:c>
       <x:c r="C94" s="0" t="s">
-        <x:v>653</x:v>
+        <x:v>659</x:v>
       </x:c>
       <x:c r="D94" s="0" t="s">
-        <x:v>654</x:v>
+        <x:v>660</x:v>
       </x:c>
       <x:c r="E94" s="0" t="s">
-        <x:v>655</x:v>
+        <x:v>661</x:v>
       </x:c>
       <x:c r="F94" s="0" t="s">
-        <x:v>656</x:v>
+        <x:v>662</x:v>
       </x:c>
       <x:c r="G94" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="H94" s="0" t="s">
-        <x:v>657</x:v>
+        <x:v>663</x:v>
       </x:c>
       <x:c r="I94" s="0" t="s">
-        <x:v>658</x:v>
+        <x:v>664</x:v>
       </x:c>
     </x:row>
     <x:row r="95" spans="1:9">
       <x:c r="A95" s="0" t="s">
-        <x:v>659</x:v>
+        <x:v>665</x:v>
       </x:c>
       <x:c r="B95" s="0" t="s">
-        <x:v>660</x:v>
+        <x:v>666</x:v>
       </x:c>
       <x:c r="C95" s="0" t="s">
-        <x:v>661</x:v>
+        <x:v>667</x:v>
       </x:c>
       <x:c r="D95" s="0" t="s">
-        <x:v>662</x:v>
+        <x:v>668</x:v>
       </x:c>
       <x:c r="E95" s="0" t="s">
-        <x:v>663</x:v>
+        <x:v>669</x:v>
       </x:c>
       <x:c r="F95" s="0" t="s">
-        <x:v>664</x:v>
+        <x:v>670</x:v>
       </x:c>
       <x:c r="G95" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="H95" s="0" t="s">
-        <x:v>665</x:v>
+        <x:v>671</x:v>
       </x:c>
       <x:c r="I95" s="0" t="s">
-        <x:v>666</x:v>
+        <x:v>672</x:v>
       </x:c>
     </x:row>
     <x:row r="96" spans="1:9">
       <x:c r="A96" s="0" t="s">
-        <x:v>667</x:v>
+        <x:v>673</x:v>
       </x:c>
       <x:c r="B96" s="0" t="s">
-        <x:v>668</x:v>
+        <x:v>674</x:v>
       </x:c>
       <x:c r="C96" s="0" t="s">
-        <x:v>669</x:v>
+        <x:v>675</x:v>
       </x:c>
       <x:c r="D96" s="0" t="s">
-        <x:v>670</x:v>
+        <x:v>676</x:v>
       </x:c>
       <x:c r="E96" s="0" t="s">
-        <x:v>671</x:v>
+        <x:v>677</x:v>
       </x:c>
       <x:c r="F96" s="0" t="s">
-        <x:v>672</x:v>
+        <x:v>678</x:v>
       </x:c>
       <x:c r="G96" s="0" t="s">
         <x:v>24</x:v>
       </x:c>
       <x:c r="H96" s="0" t="s">
-        <x:v>673</x:v>
+        <x:v>679</x:v>
       </x:c>
       <x:c r="I96" s="0" t="s">
-        <x:v>674</x:v>
+        <x:v>680</x:v>
       </x:c>
     </x:row>
     <x:row r="97" spans="1:9">
       <x:c r="A97" s="0" t="s">
-        <x:v>675</x:v>
+        <x:v>681</x:v>
       </x:c>
       <x:c r="B97" s="0" t="s">
-        <x:v>676</x:v>
+        <x:v>682</x:v>
       </x:c>
       <x:c r="C97" s="0" t="s">
-        <x:v>677</x:v>
+        <x:v>683</x:v>
       </x:c>
       <x:c r="D97" s="0" t="s">
-        <x:v>678</x:v>
+        <x:v>684</x:v>
       </x:c>
       <x:c r="E97" s="0" t="s">
-        <x:v>679</x:v>
+        <x:v>685</x:v>
       </x:c>
       <x:c r="F97" s="0" t="s">
-        <x:v>680</x:v>
+        <x:v>686</x:v>
       </x:c>
       <x:c r="G97" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="H97" s="0" t="s">
-        <x:v>681</x:v>
+        <x:v>687</x:v>
       </x:c>
       <x:c r="I97" s="0" t="s">
-        <x:v>682</x:v>
+        <x:v>688</x:v>
       </x:c>
     </x:row>
     <x:row r="98" spans="1:9">
       <x:c r="A98" s="0" t="s">
-        <x:v>683</x:v>
+        <x:v>689</x:v>
       </x:c>
       <x:c r="B98" s="0" t="s">
-        <x:v>684</x:v>
+        <x:v>690</x:v>
       </x:c>
       <x:c r="C98" s="0" t="s">
-        <x:v>685</x:v>
+        <x:v>691</x:v>
       </x:c>
       <x:c r="D98" s="0" t="s">
-        <x:v>686</x:v>
+        <x:v>692</x:v>
       </x:c>
       <x:c r="E98" s="0" t="s">
-        <x:v>663</x:v>
+        <x:v>669</x:v>
       </x:c>
       <x:c r="F98" s="0" t="s">
-        <x:v>687</x:v>
+        <x:v>693</x:v>
       </x:c>
       <x:c r="G98" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="H98" s="0" t="s">
-        <x:v>688</x:v>
+        <x:v>694</x:v>
       </x:c>
       <x:c r="I98" s="0" t="s">
-        <x:v>689</x:v>
+        <x:v>695</x:v>
       </x:c>
     </x:row>
     <x:row r="99" spans="1:9">
       <x:c r="A99" s="0" t="s">
-        <x:v>690</x:v>
+        <x:v>696</x:v>
       </x:c>
       <x:c r="B99" s="0" t="s">
-        <x:v>691</x:v>
+        <x:v>697</x:v>
       </x:c>
       <x:c r="C99" s="0" t="s">
-        <x:v>692</x:v>
+        <x:v>698</x:v>
       </x:c>
       <x:c r="D99" s="0" t="s">
-        <x:v>693</x:v>
+        <x:v>699</x:v>
       </x:c>
       <x:c r="E99" s="0" t="s">
-        <x:v>663</x:v>
+        <x:v>669</x:v>
       </x:c>
       <x:c r="F99" s="0" t="s">
-        <x:v>694</x:v>
+        <x:v>700</x:v>
       </x:c>
       <x:c r="G99" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="H99" s="0" t="s">
-        <x:v>695</x:v>
+        <x:v>701</x:v>
       </x:c>
       <x:c r="I99" s="0" t="s">
-        <x:v>696</x:v>
+        <x:v>702</x:v>
       </x:c>
     </x:row>
     <x:row r="100" spans="1:9">
       <x:c r="A100" s="0" t="s">
-        <x:v>697</x:v>
+        <x:v>703</x:v>
       </x:c>
       <x:c r="B100" s="0" t="s">
-        <x:v>698</x:v>
+        <x:v>704</x:v>
       </x:c>
       <x:c r="C100" s="0" t="s">
-        <x:v>699</x:v>
+        <x:v>705</x:v>
       </x:c>
       <x:c r="D100" s="0" t="s">
-        <x:v>700</x:v>
+        <x:v>706</x:v>
       </x:c>
       <x:c r="E100" s="0" t="s">
-        <x:v>701</x:v>
+        <x:v>707</x:v>
       </x:c>
       <x:c r="F100" s="0" t="s">
-        <x:v>702</x:v>
+        <x:v>708</x:v>
       </x:c>
       <x:c r="G100" s="0" t="s">
         <x:v>15</x:v>
       </x:c>
       <x:c r="H100" s="0" t="s">
-        <x:v>703</x:v>
+        <x:v>709</x:v>
       </x:c>
       <x:c r="I100" s="0" t="s">
-        <x:v>704</x:v>
+        <x:v>710</x:v>
       </x:c>
     </x:row>
   </x:sheetData>
